--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -847,8 +847,10 @@
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>10266237</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>10266237.0</t>
+        </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -891,7 +893,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,13 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="SansSerif"/>
@@ -358,7 +365,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -368,39 +375,39 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -779,7 +786,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -796,7 +803,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>PK003702845543</t>
+          <t>PK003702920736</t>
         </is>
       </c>
     </row>
@@ -826,7 +833,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>115338833</v>
+        <v>2007111196</v>
       </c>
     </row>
     <row r="7">
@@ -838,7 +845,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>115338833</v>
+        <v>2007111196</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +854,8 @@
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>10266237.0</t>
-        </is>
+      <c r="D8" s="4" t="n">
+        <v>10266237</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -888,12 +893,12 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>PK003702845543</t>
+          <t>PK003702920736</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -902,7 +907,7 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>115338833</v>
+        <v>2007111196</v>
       </c>
     </row>
     <row r="13"/>
@@ -955,16 +960,16 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>PMP1266517</t>
+          <t>PMP1285642</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>81057613</v>
+        <v>3716132.28</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>81057613</v>
+        <v>3716132.28</v>
       </c>
       <c r="I19" s="11" t="inlineStr"/>
     </row>
@@ -976,16 +981,16 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>PMP1266518</t>
+          <t>PMP1285643</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1102345</v>
+        <v>1631086.4</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>1102345</v>
+        <v>1631086.4</v>
       </c>
       <c r="I20" s="11" t="inlineStr"/>
     </row>
@@ -997,16 +1002,16 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>PMP1266519</t>
+          <t>PMP1285644</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>71132191</v>
+        <v>1953787.6</v>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>71132191</v>
+        <v>1953787.6</v>
       </c>
       <c r="I21" s="11" t="inlineStr"/>
     </row>
@@ -1018,16 +1023,16 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1266520</t>
+          <t>PMP1285645</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>14092364</v>
+        <v>3716132.28</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>14092364</v>
+        <v>3716132.28</v>
       </c>
       <c r="I22" s="11" t="inlineStr"/>
     </row>
@@ -1039,16 +1044,16 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1266521</t>
+          <t>PMP1286181</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>661407</v>
+        <v>96593393.26000001</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="6" t="n">
-        <v>661407</v>
+        <v>96593393.26000001</v>
       </c>
       <c r="I23" s="11" t="inlineStr"/>
     </row>
@@ -1060,16 +1065,16 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1266522</t>
+          <t>PMP1286182</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>11096370</v>
+        <v>70799635.87</v>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
       <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>11096370</v>
+        <v>70799635.87</v>
       </c>
       <c r="I24" s="11" t="inlineStr"/>
     </row>
@@ -1081,16 +1086,16 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>PMP1266989</t>
+          <t>PMP1286191</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>10648056</v>
+        <v>468865394.64</v>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>10648056</v>
+        <v>468865394.64</v>
       </c>
       <c r="I25" s="11" t="inlineStr"/>
     </row>
@@ -1102,16 +1107,16 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>PMP1266990</t>
+          <t>PMP1286379</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1763751</v>
+        <v>15060953.5</v>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>1763751</v>
+        <v>15060953.5</v>
       </c>
       <c r="I26" s="11" t="inlineStr"/>
     </row>
@@ -1123,16 +1128,16 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PMP1266991</t>
+          <t>PMP1286380</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>47972873</v>
+        <v>3569198.36</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>47972873</v>
+        <v>3569198.36</v>
       </c>
       <c r="I27" s="11" t="inlineStr"/>
     </row>
@@ -1144,16 +1149,16 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>PMP1266992</t>
+          <t>PMP1286421</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>54353501</v>
+        <v>10003422.2</v>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="6" t="n">
-        <v>54353501</v>
+        <v>10003422.2</v>
       </c>
       <c r="I28" s="11" t="inlineStr"/>
     </row>
@@ -1165,16 +1170,16 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>PMP1266993</t>
+          <t>PMP1286422</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>7545532</v>
+        <v>280714498.44</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>7545532</v>
+        <v>280714498.44</v>
       </c>
       <c r="I29" s="11" t="inlineStr"/>
     </row>
@@ -1186,16 +1191,16 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>PMP1267064</t>
+          <t>PMP1286464</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7802451</v>
+        <v>2371651</v>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
       <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="6" t="n">
-        <v>7802451</v>
+        <v>2371651</v>
       </c>
       <c r="I30" s="11" t="inlineStr"/>
     </row>
@@ -1207,16 +1212,16 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>PMP1267065</t>
+          <t>PMP1286465</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>32139462</v>
+        <v>62624115.22</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>32139462</v>
+        <v>62624115.22</v>
       </c>
       <c r="I31" s="11" t="inlineStr"/>
     </row>
@@ -1228,16 +1233,16 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>PMP1267066</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>36393214</v>
+        <v>640693961.84</v>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="6" t="n">
-        <v>36393214</v>
+        <v>640693961.84</v>
       </c>
       <c r="I32" s="11" t="inlineStr"/>
     </row>
@@ -1249,16 +1254,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PMP1267067</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>13978207</v>
+        <v>640693961.84</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>13978207</v>
+        <v>640693961.84</v>
       </c>
       <c r="I33" s="11" t="inlineStr"/>
     </row>
@@ -1270,16 +1275,16 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PMP1267068</t>
+          <t>PMP1286467</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>10918828</v>
+        <v>137894507.16</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>10918828</v>
+        <v>137894507.16</v>
       </c>
       <c r="I34" s="11" t="inlineStr"/>
     </row>
@@ -1291,16 +1296,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>PMP1267239</t>
+          <t>PMP1291552</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>24772082.74</v>
+        <v>4175700</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>24772082.74</v>
+        <v>4175700</v>
       </c>
       <c r="I35" s="11" t="inlineStr"/>
     </row>
@@ -1312,16 +1317,16 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>PMP1267240</t>
+          <t>PMP1291553</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>47305349.16</v>
+        <v>41784946.6</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>47305349.16</v>
+        <v>41784946.6</v>
       </c>
       <c r="I36" s="11" t="inlineStr"/>
     </row>
@@ -1333,16 +1338,16 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PMP1267241</t>
+          <t>PMP1291554</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>18259552.84</v>
+        <v>1230911.12</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>18259552.84</v>
+        <v>1230911.12</v>
       </c>
       <c r="I37" s="11" t="inlineStr"/>
     </row>
@@ -1354,16 +1359,16 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>PMP1267242</t>
+          <t>PMP1291555</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>2037042</v>
+        <v>347975</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>2037042</v>
+        <v>347975</v>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
     </row>
@@ -1375,544 +1380,1246 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMP1267243</t>
+          <t>PMP1291556</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>18134889.5</v>
+        <v>47200684.8</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>18134889.5</v>
+        <v>47200684.8</v>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>4634650314</t>
+          <t>PMP1291557</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-65751</v>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>173988</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>-65751</v>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>AVERIA 4634650314</t>
-        </is>
-      </c>
+        <v>173988</v>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>4634979239</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>-13931</v>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>554871.24</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>-13931</v>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>AVERIA 4634979239</t>
-        </is>
-      </c>
+        <v>554871.24</v>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>4635062908</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-10001</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>7395026.5</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>-10001</v>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>AVERIA 4635062908</t>
-        </is>
-      </c>
+        <v>7395026.5</v>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>0085495759</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-132223870</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>62932310.75</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>-132223870</v>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085495759</t>
-        </is>
-      </c>
+        <v>62932310.75</v>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>9801662646</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-260735350</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>FACT PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>CSB</t>
-        </is>
-      </c>
+        <v>43153234.4</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>-260735350</v>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>FACT PROVEEDOR 9801662646</t>
-        </is>
-      </c>
+        <v>43153234.4</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>PMP1266517</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-228</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>43153234.4</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
       <c r="H45" s="6" t="n">
-        <v>-228</v>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266517</t>
-        </is>
-      </c>
+        <v>43153234.4</v>
+      </c>
+      <c r="I45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>PMP1266519</t>
+          <t>PMP1291562</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>7043898.34</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>-200</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266519</t>
-        </is>
-      </c>
+        <v>7043898.34</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PMP1266522</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>-1596332</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>82462889.81999999</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr"/>
+      <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>-1596332</v>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266522</t>
-        </is>
-      </c>
+        <v>82462889.81999999</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>PMP1266991</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-135</v>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>7349759</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr"/>
+      <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="6" t="n">
-        <v>-135</v>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266991</t>
-        </is>
-      </c>
+        <v>7349759</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>PMP1266992</t>
+          <t>PMP1292294</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-153</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>3131775</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>-153</v>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266992</t>
-        </is>
-      </c>
+        <v>3131775</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>PMP1266993</t>
+          <t>PMP1292295</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-1085506</v>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>86994</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
       <c r="H50" s="6" t="n">
-        <v>-1085506</v>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1266993</t>
-        </is>
-      </c>
+        <v>86994</v>
+      </c>
+      <c r="I50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>PMP1267065</t>
+          <t>PMP1292296</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-90</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>13811678.4</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr"/>
+      <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="6" t="n">
-        <v>-90</v>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1267065</t>
-        </is>
-      </c>
+        <v>13811678.4</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>PMP1267066</t>
+          <t>PMP1292297</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>-103</v>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>32030709.54</v>
+      </c>
+      <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="6" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1267066</t>
-        </is>
-      </c>
+        <v>32030709.54</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>PMP1267068</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>-1570791</v>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>34758234.75</v>
+      </c>
+      <c r="F53" s="10" t="inlineStr"/>
+      <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="6" t="n">
-        <v>-1570791</v>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1267068</t>
-        </is>
-      </c>
+        <v>34758234.75</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>PMP1267239</t>
+          <t>PMP1292309</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>-441292</v>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+        <v>20376764.8</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="6" t="n">
-        <v>-441292</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1267239</t>
-        </is>
-      </c>
+        <v>20376764.8</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="C55" s="10" t="inlineStr">
         <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292593</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>3131775</v>
+      </c>
+      <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="10" t="inlineStr"/>
+      <c r="H55" s="6" t="n">
+        <v>3131775</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292594</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>30380459.6</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="10" t="inlineStr"/>
+      <c r="H56" s="6" t="n">
+        <v>30380459.6</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292652</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>30145687</v>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="10" t="inlineStr"/>
+      <c r="H57" s="6" t="n">
+        <v>30145687</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292653</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>27925238.47</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr"/>
+      <c r="G58" s="10" t="inlineStr"/>
+      <c r="H58" s="6" t="n">
+        <v>27925238.47</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292654</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>46242233.5</v>
+      </c>
+      <c r="F59" s="10" t="inlineStr"/>
+      <c r="G59" s="10" t="inlineStr"/>
+      <c r="H59" s="6" t="n">
+        <v>46242233.5</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292704</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>4192184.8</v>
+      </c>
+      <c r="F60" s="10" t="inlineStr"/>
+      <c r="G60" s="10" t="inlineStr"/>
+      <c r="H60" s="6" t="n">
+        <v>4192184.8</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292712</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>16403804</v>
+      </c>
+      <c r="F61" s="10" t="inlineStr"/>
+      <c r="G61" s="10" t="inlineStr"/>
+      <c r="H61" s="6" t="n">
+        <v>16403804</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292713</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>31007952.84</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="10" t="inlineStr"/>
+      <c r="H62" s="6" t="n">
+        <v>31007952.84</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292714</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>32461435</v>
+      </c>
+      <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="6" t="n">
+        <v>32461435</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>4636412647</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>-16320</v>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>-16320</v>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>AVERIA 4636412647</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>0085501420</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>-11077235</v>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>-11077235</v>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>DESCUENTO 0085501420</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>9801673296</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>-116500000</v>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>CSB</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>-116500000</v>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR 9801673296</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>9801673633</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>-296234085</v>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>CSB</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>-296234085</v>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR 9801673633</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
           <t>Descuentos Clientes</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>PMP1267243</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>-84475</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>-81.3200000107754</v>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>-81.3200000107754</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>PMP1286466</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>-636309101.84</v>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Menor Vlr Pagado</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>-636309101.84</v>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Menor Vlr Pagado PMP1286466</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291561</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>-42283834.4</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Menor Vlr Pagado</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>-42283834.4</v>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Menor Vlr Pagado PMP1291561</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>PMP1286182</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>-232158</v>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>RECHAZO</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>551</t>
         </is>
       </c>
-      <c r="H55" s="6" t="n">
-        <v>-84475</v>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1267243</t>
+      <c r="H71" s="6" t="n">
+        <v>-232158</v>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1286182</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>PMP1286191</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>-474381</v>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>-474381</v>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1286191</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>PMP1286466</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>-4623481</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>-4623481</v>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1286466</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291558</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291558</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291559</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>-94939</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>-94939</v>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291559</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291560</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>-1101</v>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>-1101</v>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291560</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291561</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>-869290</v>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>-869290</v>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291561</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291563</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>-8705</v>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>-8705</v>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291563</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>PMP1291965</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>-153246</v>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>-153246</v>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1291965</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292298</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>-608</v>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>-608</v>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292298</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292652</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>-143</v>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>-143</v>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292652</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292654</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>-808</v>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>-808</v>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292654</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292712</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>-68</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292712</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292713</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292713</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>PMP1292714</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>-567</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>RECHAZO</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>-567</v>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>RECHAZO PMP1292714</t>
         </is>
       </c>
     </row>
@@ -1927,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.33203125" customWidth="1" min="1" max="1"/>
@@ -2022,7 +2729,7 @@
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>00596131</t>
+          <t>00603928</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -2032,7 +2739,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>06-10-2025</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="G3" s="14" t="n"/>
@@ -2234,7 +2941,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>PK003702845543</t>
+          <t>PK003702920736</t>
         </is>
       </c>
       <c r="G8" s="14" t="n"/>
@@ -2267,7 +2974,11 @@
           <t>Medio de Pago:</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pago a una cuenta bancaria </t>
+        </is>
+      </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Nro Cheque:</t>
@@ -2275,7 +2986,7 @@
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>3702845543</t>
+          <t>3702920736</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -2322,7 +3033,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>06-10-2025</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="E10" s="20" t="n"/>
@@ -2402,7 +3113,11 @@
           <t>Canal de Pago:</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n"/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Pago por otras redes de transmisión, p. e. La red privada de institución financiera</t>
+        </is>
+      </c>
       <c r="E12" s="20" t="n"/>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="14" t="n"/>
@@ -2908,20 +3623,24 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n"/>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C23" s="29" t="inlineStr">
         <is>
-          <t>2103805704</t>
+          <t>2102261255</t>
         </is>
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>0085495759001</t>
+          <t>0085501420001</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>25-09-2025</t>
+          <t>19-11-2025</t>
         </is>
       </c>
       <c r="F23" s="29" t="n"/>
@@ -2942,12 +3661,12 @@
       <c r="M23" s="29" t="n"/>
       <c r="N23" s="29" t="inlineStr">
         <is>
-          <t>-132.223.870,00</t>
+          <t>-11.077.235,00</t>
         </is>
       </c>
       <c r="O23" s="29" t="inlineStr">
         <is>
-          <t>-132.223.870,00</t>
+          <t>-11.077.235,00</t>
         </is>
       </c>
       <c r="P23" s="29" t="inlineStr">
@@ -3015,31 +3734,39 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n"/>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>5213920875</t>
+          <t>5213944761</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>4634650314001</t>
+          <t>4636412647001</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>27-09-2025</t>
+          <t>18-11-2025</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>7701008003194</t>
-        </is>
-      </c>
-      <c r="G24" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>4634650314</t>
+          <t>4636412647</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
@@ -3057,12 +3784,12 @@
       <c r="M24" s="29" t="n"/>
       <c r="N24" s="29" t="inlineStr">
         <is>
-          <t>-65.751,00</t>
+          <t>-16.320,00</t>
         </is>
       </c>
       <c r="O24" s="29" t="inlineStr">
         <is>
-          <t>-55.253,00</t>
+          <t>-13.714,00</t>
         </is>
       </c>
       <c r="P24" s="29" t="inlineStr">
@@ -3072,7 +3799,7 @@
       </c>
       <c r="Q24" s="29" t="inlineStr">
         <is>
-          <t>-10.498,00</t>
+          <t>-2.606,00</t>
         </is>
       </c>
       <c r="R24" s="29" t="inlineStr">
@@ -3130,33 +3857,29 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n"/>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C25" s="29" t="inlineStr">
         <is>
-          <t>5213918945</t>
+          <t>2103760933</t>
         </is>
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>4634979239001</t>
+          <t>9801673296001</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>26-09-2025</t>
-        </is>
-      </c>
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>7701008006263</t>
-        </is>
-      </c>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="n"/>
       <c r="G25" s="29" t="n"/>
-      <c r="H25" s="29" t="inlineStr">
-        <is>
-          <t>4634979239</t>
-        </is>
-      </c>
+      <c r="H25" s="29" t="n"/>
       <c r="I25" s="29" t="inlineStr">
         <is>
           <t>0</t>
@@ -3172,12 +3895,12 @@
       <c r="M25" s="29" t="n"/>
       <c r="N25" s="29" t="inlineStr">
         <is>
-          <t>-13.931,00</t>
+          <t>-116.500.000,00</t>
         </is>
       </c>
       <c r="O25" s="29" t="inlineStr">
         <is>
-          <t>-11.707,00</t>
+          <t>-100.000.000,00</t>
         </is>
       </c>
       <c r="P25" s="29" t="inlineStr">
@@ -3187,7 +3910,7 @@
       </c>
       <c r="Q25" s="29" t="inlineStr">
         <is>
-          <t>-2.224,00</t>
+          <t>-19.000.000,00</t>
         </is>
       </c>
       <c r="R25" s="29" t="inlineStr">
@@ -3202,7 +3925,7 @@
       </c>
       <c r="T25" s="29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.500.000,00</t>
         </is>
       </c>
       <c r="U25" s="29" t="inlineStr">
@@ -3245,33 +3968,29 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>5213877993</t>
+          <t>2103626424</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>4635062908001</t>
+          <t>9801673633001</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>30-09-2025</t>
-        </is>
-      </c>
-      <c r="F26" s="29" t="inlineStr">
-        <is>
-          <t>7701008109001</t>
-        </is>
-      </c>
+          <t>20-11-2025</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="n"/>
       <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="inlineStr">
-        <is>
-          <t>4635062908</t>
-        </is>
-      </c>
+      <c r="H26" s="29" t="n"/>
       <c r="I26" s="29" t="inlineStr">
         <is>
           <t>0</t>
@@ -3287,12 +4006,12 @@
       <c r="M26" s="29" t="n"/>
       <c r="N26" s="29" t="inlineStr">
         <is>
-          <t>-10.001,00</t>
+          <t>-296.234.085,00</t>
         </is>
       </c>
       <c r="O26" s="29" t="inlineStr">
         <is>
-          <t>-8.404,00</t>
+          <t>-257.594.856,00</t>
         </is>
       </c>
       <c r="P26" s="29" t="inlineStr">
@@ -3302,7 +4021,7 @@
       </c>
       <c r="Q26" s="29" t="inlineStr">
         <is>
-          <t>-1.597,00</t>
+          <t>-48.943.023,00</t>
         </is>
       </c>
       <c r="R26" s="29" t="inlineStr">
@@ -3317,7 +4036,7 @@
       </c>
       <c r="T26" s="29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.303.794,00</t>
         </is>
       </c>
       <c r="U26" s="29" t="inlineStr">
@@ -3357,28 +4076,44 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C27" s="29" t="inlineStr">
         <is>
-          <t>2103646445</t>
+          <t>5213886624</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>9801662646001</t>
+          <t>CD4628436910001</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>24-09-2025</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
+          <t>25-10-2025</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>7701008106109</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STO 610 24 HORAS                       </t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>4635666906</t>
+        </is>
+      </c>
       <c r="I27" s="29" t="inlineStr">
         <is>
           <t>0</t>
@@ -3394,12 +4129,12 @@
       <c r="M27" s="29" t="n"/>
       <c r="N27" s="29" t="inlineStr">
         <is>
-          <t>-260.735.350,00</t>
+          <t>43.176,00</t>
         </is>
       </c>
       <c r="O27" s="29" t="inlineStr">
         <is>
-          <t>-226.726.392,00</t>
+          <t>36.282,00</t>
         </is>
       </c>
       <c r="P27" s="29" t="inlineStr">
@@ -3409,7 +4144,7 @@
       </c>
       <c r="Q27" s="29" t="inlineStr">
         <is>
-          <t>-43.078.014,00</t>
+          <t>6.894,00</t>
         </is>
       </c>
       <c r="R27" s="29" t="inlineStr">
@@ -3424,7 +4159,7 @@
       </c>
       <c r="T27" s="29" t="inlineStr">
         <is>
-          <t>9.069.056,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="U27" s="29" t="inlineStr">
@@ -3464,23 +4199,27 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>5313645314</t>
+          <t>5133799732</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>PMP1266517001</t>
+          <t>PMP1285642001</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>11-09-2025</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
@@ -3488,10 +4227,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G28" s="29" t="n"/>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>4633134633</t>
+          <t>4634517345</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
@@ -3509,12 +4252,12 @@
       <c r="M28" s="29" t="n"/>
       <c r="N28" s="29" t="inlineStr">
         <is>
-          <t>-228,00</t>
+          <t>3.716.056,00</t>
         </is>
       </c>
       <c r="O28" s="29" t="inlineStr">
         <is>
-          <t>-192,00</t>
+          <t>3.204.509,00</t>
         </is>
       </c>
       <c r="P28" s="29" t="inlineStr">
@@ -3524,7 +4267,7 @@
       </c>
       <c r="Q28" s="29" t="inlineStr">
         <is>
-          <t>-36,00</t>
+          <t>511.547,00</t>
         </is>
       </c>
       <c r="R28" s="29" t="inlineStr">
@@ -3582,20 +4325,24 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n"/>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C29" s="29" t="inlineStr">
         <is>
-          <t>5133742850</t>
+          <t>5133971843</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>PMP1266517002</t>
+          <t>PMP1285643001</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>11-09-2025</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
@@ -3603,10 +4350,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G29" s="29" t="n"/>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>4633134633</t>
+          <t>4634472026</t>
         </is>
       </c>
       <c r="I29" s="29" t="inlineStr">
@@ -3624,12 +4375,12 @@
       <c r="M29" s="29" t="n"/>
       <c r="N29" s="29" t="inlineStr">
         <is>
-          <t>81.057.612,00</t>
+          <t>1.631.086,00</t>
         </is>
       </c>
       <c r="O29" s="29" t="inlineStr">
         <is>
-          <t>69.977.790,00</t>
+          <t>1.370.661,00</t>
         </is>
       </c>
       <c r="P29" s="29" t="inlineStr">
@@ -3639,7 +4390,7 @@
       </c>
       <c r="Q29" s="29" t="inlineStr">
         <is>
-          <t>11.079.822,00</t>
+          <t>260.425,00</t>
         </is>
       </c>
       <c r="R29" s="29" t="inlineStr">
@@ -3697,20 +4448,24 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n"/>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>5133694225</t>
+          <t>5133844476</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>PMP1266518001</t>
+          <t>PMP1285644001</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>11-09-2025</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
@@ -3718,10 +4473,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G30" s="29" t="n"/>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>4633068611</t>
+          <t>4634542434</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
@@ -3739,12 +4498,12 @@
       <c r="M30" s="29" t="n"/>
       <c r="N30" s="29" t="inlineStr">
         <is>
-          <t>1.102.345,00</t>
+          <t>1.953.787,00</t>
         </is>
       </c>
       <c r="O30" s="29" t="inlineStr">
         <is>
-          <t>926.340,00</t>
+          <t>1.641.838,00</t>
         </is>
       </c>
       <c r="P30" s="29" t="inlineStr">
@@ -3754,7 +4513,7 @@
       </c>
       <c r="Q30" s="29" t="inlineStr">
         <is>
-          <t>176.005,00</t>
+          <t>311.949,00</t>
         </is>
       </c>
       <c r="R30" s="29" t="inlineStr">
@@ -3809,23 +4568,27 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C31" s="29" t="inlineStr">
         <is>
-          <t>5314096848</t>
+          <t>5133801635</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>PMP1266519001</t>
+          <t>PMP1285645001</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>11-09-2025</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
@@ -3833,10 +4596,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G31" s="29" t="n"/>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>4633143029</t>
+          <t>4634472027</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
@@ -3854,12 +4621,12 @@
       <c r="M31" s="29" t="n"/>
       <c r="N31" s="29" t="inlineStr">
         <is>
-          <t>-200,00</t>
+          <t>3.716.130,00</t>
         </is>
       </c>
       <c r="O31" s="29" t="inlineStr">
         <is>
-          <t>-168,00</t>
+          <t>3.205.045,00</t>
         </is>
       </c>
       <c r="P31" s="29" t="inlineStr">
@@ -3869,7 +4636,7 @@
       </c>
       <c r="Q31" s="29" t="inlineStr">
         <is>
-          <t>-32,00</t>
+          <t>511.085,00</t>
         </is>
       </c>
       <c r="R31" s="29" t="inlineStr">
@@ -3927,31 +4694,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n"/>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>5133683268</t>
+          <t>5133895452</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>PMP1266519002</t>
+          <t>PMP1286181001</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>7701008109001</t>
-        </is>
-      </c>
-      <c r="G32" s="29" t="n"/>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>4633143029</t>
+          <t>4634572510</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
@@ -3969,12 +4744,12 @@
       <c r="M32" s="29" t="n"/>
       <c r="N32" s="29" t="inlineStr">
         <is>
-          <t>71.132.191,00</t>
+          <t>96.593.393,00</t>
         </is>
       </c>
       <c r="O32" s="29" t="inlineStr">
         <is>
-          <t>61.409.081,00</t>
+          <t>81.170.918,00</t>
         </is>
       </c>
       <c r="P32" s="29" t="inlineStr">
@@ -3984,7 +4759,7 @@
       </c>
       <c r="Q32" s="29" t="inlineStr">
         <is>
-          <t>9.723.110,00</t>
+          <t>15.422.475,00</t>
         </is>
       </c>
       <c r="R32" s="29" t="inlineStr">
@@ -4042,31 +4817,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n"/>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C33" s="29" t="inlineStr">
         <is>
-          <t>5132226456</t>
+          <t>5133912287</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>PMP1266520001</t>
+          <t>PMP1286182001</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>7701008109001</t>
-        </is>
-      </c>
-      <c r="G33" s="29" t="n"/>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>4633011579</t>
+          <t>4634572516</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
@@ -4084,12 +4867,12 @@
       <c r="M33" s="29" t="n"/>
       <c r="N33" s="29" t="inlineStr">
         <is>
-          <t>14.092.365,00</t>
+          <t>70.799.634,00</t>
         </is>
       </c>
       <c r="O33" s="29" t="inlineStr">
         <is>
-          <t>12.166.083,00</t>
+          <t>59.495.491,00</t>
         </is>
       </c>
       <c r="P33" s="29" t="inlineStr">
@@ -4099,7 +4882,7 @@
       </c>
       <c r="Q33" s="29" t="inlineStr">
         <is>
-          <t>1.926.282,00</t>
+          <t>11.304.143,00</t>
         </is>
       </c>
       <c r="R33" s="29" t="inlineStr">
@@ -4154,34 +4937,42 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="n"/>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>5133638716</t>
+          <t>5314134150</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>PMP1266521001</t>
+          <t>PMP1286182002</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>7701008109001</t>
-        </is>
-      </c>
-      <c r="G34" s="29" t="n"/>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>4633011577</t>
+          <t>4634572516</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
@@ -4199,12 +4990,12 @@
       <c r="M34" s="29" t="n"/>
       <c r="N34" s="29" t="inlineStr">
         <is>
-          <t>661.407,00</t>
+          <t>-232.158,00</t>
         </is>
       </c>
       <c r="O34" s="29" t="inlineStr">
         <is>
-          <t>555.804,00</t>
+          <t>-195.091,00</t>
         </is>
       </c>
       <c r="P34" s="29" t="inlineStr">
@@ -4214,7 +5005,7 @@
       </c>
       <c r="Q34" s="29" t="inlineStr">
         <is>
-          <t>105.603,00</t>
+          <t>-37.067,00</t>
         </is>
       </c>
       <c r="R34" s="29" t="inlineStr">
@@ -4269,23 +5060,27 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C35" s="29" t="inlineStr">
         <is>
-          <t>5314146517</t>
+          <t>5133742728</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>PMP1266522001</t>
+          <t>PMP1286191001</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
@@ -4293,10 +5088,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G35" s="29" t="n"/>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>4633212276</t>
+          <t>4634614438</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
@@ -4314,12 +5113,12 @@
       <c r="M35" s="29" t="n"/>
       <c r="N35" s="29" t="inlineStr">
         <is>
-          <t>-1.596.332,00</t>
+          <t>468.865.395,00</t>
         </is>
       </c>
       <c r="O35" s="29" t="inlineStr">
         <is>
-          <t>-1.341.455,00</t>
+          <t>404.764.964,00</t>
         </is>
       </c>
       <c r="P35" s="29" t="inlineStr">
@@ -4329,7 +5128,7 @@
       </c>
       <c r="Q35" s="29" t="inlineStr">
         <is>
-          <t>-254.877,00</t>
+          <t>64.100.431,00</t>
         </is>
       </c>
       <c r="R35" s="29" t="inlineStr">
@@ -4384,23 +5183,27 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="B36" s="29" t="n"/>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>5133728036</t>
+          <t>5314058061</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>PMP1266522002</t>
+          <t>PMP1286191002</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
@@ -4408,10 +5211,14 @@
           <t>7701008109001</t>
         </is>
       </c>
-      <c r="G36" s="29" t="n"/>
+      <c r="G36" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>4633212276</t>
+          <t>4634614438</t>
         </is>
       </c>
       <c r="I36" s="29" t="inlineStr">
@@ -4429,12 +5236,12 @@
       <c r="M36" s="29" t="n"/>
       <c r="N36" s="29" t="inlineStr">
         <is>
-          <t>11.096.370,00</t>
+          <t>-474.381,00</t>
         </is>
       </c>
       <c r="O36" s="29" t="inlineStr">
         <is>
-          <t>9.324.680,00</t>
+          <t>-398.639,00</t>
         </is>
       </c>
       <c r="P36" s="29" t="inlineStr">
@@ -4444,7 +5251,7 @@
       </c>
       <c r="Q36" s="29" t="inlineStr">
         <is>
-          <t>1.771.690,00</t>
+          <t>-75.742,00</t>
         </is>
       </c>
       <c r="R36" s="29" t="inlineStr">
@@ -4502,31 +5309,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n"/>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C37" s="29" t="inlineStr">
         <is>
-          <t>5133652700</t>
+          <t>5133869561</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>PMP1266989001</t>
+          <t>PMP1286379001</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G37" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G37" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>4633074804</t>
+          <t>4634517341</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
@@ -4544,12 +5359,12 @@
       <c r="M37" s="29" t="n"/>
       <c r="N37" s="29" t="inlineStr">
         <is>
-          <t>10.648.056,00</t>
+          <t>15.060.956,00</t>
         </is>
       </c>
       <c r="O37" s="29" t="inlineStr">
         <is>
-          <t>9.192.576,00</t>
+          <t>12.656.266,00</t>
         </is>
       </c>
       <c r="P37" s="29" t="inlineStr">
@@ -4559,7 +5374,7 @@
       </c>
       <c r="Q37" s="29" t="inlineStr">
         <is>
-          <t>1.455.480,00</t>
+          <t>2.404.690,00</t>
         </is>
       </c>
       <c r="R37" s="29" t="inlineStr">
@@ -4617,31 +5432,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n"/>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>5133735901</t>
+          <t>5133933050</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>PMP1266990001</t>
+          <t>PMP1286380001</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G38" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G38" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>4633074802</t>
+          <t>4634517341</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
@@ -4659,12 +5482,12 @@
       <c r="M38" s="29" t="n"/>
       <c r="N38" s="29" t="inlineStr">
         <is>
-          <t>1.763.751,00</t>
+          <t>3.569.201,00</t>
         </is>
       </c>
       <c r="O38" s="29" t="inlineStr">
         <is>
-          <t>1.482.144,00</t>
+          <t>2.999.329,00</t>
         </is>
       </c>
       <c r="P38" s="29" t="inlineStr">
@@ -4674,7 +5497,7 @@
       </c>
       <c r="Q38" s="29" t="inlineStr">
         <is>
-          <t>281.607,00</t>
+          <t>569.872,00</t>
         </is>
       </c>
       <c r="R38" s="29" t="inlineStr">
@@ -4732,20 +5555,24 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n"/>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>5133743892</t>
+          <t>5133806493</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>PMP1266991001</t>
+          <t>PMP1286421001</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
@@ -4753,10 +5580,14 @@
           <t>7701008009455</t>
         </is>
       </c>
-      <c r="G39" s="29" t="n"/>
+      <c r="G39" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>4633143032</t>
+          <t>4634572513</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
@@ -4774,12 +5605,12 @@
       <c r="M39" s="29" t="n"/>
       <c r="N39" s="29" t="inlineStr">
         <is>
-          <t>47.972.873,00</t>
+          <t>10.003.422,00</t>
         </is>
       </c>
       <c r="O39" s="29" t="inlineStr">
         <is>
-          <t>41.415.427,00</t>
+          <t>8.406.237,00</t>
         </is>
       </c>
       <c r="P39" s="29" t="inlineStr">
@@ -4789,7 +5620,7 @@
       </c>
       <c r="Q39" s="29" t="inlineStr">
         <is>
-          <t>6.557.446,00</t>
+          <t>1.597.185,00</t>
         </is>
       </c>
       <c r="R39" s="29" t="inlineStr">
@@ -4844,23 +5675,27 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>5314051063</t>
+          <t>5133953006</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>PMP1266991002</t>
+          <t>PMP1286422001</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
@@ -4868,10 +5703,14 @@
           <t>7701008009455</t>
         </is>
       </c>
-      <c r="G40" s="29" t="n"/>
+      <c r="G40" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>4633143032</t>
+          <t>4634572515</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
@@ -4889,12 +5728,12 @@
       <c r="M40" s="29" t="n"/>
       <c r="N40" s="29" t="inlineStr">
         <is>
-          <t>-135,00</t>
+          <t>280.714.500,00</t>
         </is>
       </c>
       <c r="O40" s="29" t="inlineStr">
         <is>
-          <t>-114,00</t>
+          <t>242.343.401,00</t>
         </is>
       </c>
       <c r="P40" s="29" t="inlineStr">
@@ -4904,7 +5743,7 @@
       </c>
       <c r="Q40" s="29" t="inlineStr">
         <is>
-          <t>-21,00</t>
+          <t>38.371.099,00</t>
         </is>
       </c>
       <c r="R40" s="29" t="inlineStr">
@@ -4962,31 +5801,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n"/>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C41" s="29" t="inlineStr">
         <is>
-          <t>5133735900</t>
+          <t>5133910058</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>PMP1266992001</t>
+          <t>PMP1286464001</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G41" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>4633102737</t>
+          <t>4634614434</t>
         </is>
       </c>
       <c r="I41" s="29" t="inlineStr">
@@ -5004,12 +5851,12 @@
       <c r="M41" s="29" t="n"/>
       <c r="N41" s="29" t="inlineStr">
         <is>
-          <t>54.353.501,00</t>
+          <t>2.371.651,00</t>
         </is>
       </c>
       <c r="O41" s="29" t="inlineStr">
         <is>
-          <t>46.923.882,00</t>
+          <t>1.992.984,00</t>
         </is>
       </c>
       <c r="P41" s="29" t="inlineStr">
@@ -5019,7 +5866,7 @@
       </c>
       <c r="Q41" s="29" t="inlineStr">
         <is>
-          <t>7.429.619,00</t>
+          <t>378.667,00</t>
         </is>
       </c>
       <c r="R41" s="29" t="inlineStr">
@@ -5074,34 +5921,42 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B42" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>5314125697</t>
+          <t>5133970855</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>PMP1266992002</t>
+          <t>PMP1286465001</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G42" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G42" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>4633102737</t>
+          <t>4634614440</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
@@ -5119,12 +5974,12 @@
       <c r="M42" s="29" t="n"/>
       <c r="N42" s="29" t="inlineStr">
         <is>
-          <t>-153,00</t>
+          <t>62.624.114,00</t>
         </is>
       </c>
       <c r="O42" s="29" t="inlineStr">
         <is>
-          <t>-128,00</t>
+          <t>52.625.306,00</t>
         </is>
       </c>
       <c r="P42" s="29" t="inlineStr">
@@ -5134,7 +5989,7 @@
       </c>
       <c r="Q42" s="29" t="inlineStr">
         <is>
-          <t>-25,00</t>
+          <t>9.998.808,00</t>
         </is>
       </c>
       <c r="R42" s="29" t="inlineStr">
@@ -5192,31 +6047,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n"/>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C43" s="29" t="inlineStr">
         <is>
-          <t>5133752806</t>
+          <t>5133781746</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>PMP1266993001</t>
+          <t>PMP1286466001</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G43" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G43" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>4633161077</t>
+          <t>4634614433</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
@@ -5234,12 +6097,12 @@
       <c r="M43" s="29" t="n"/>
       <c r="N43" s="29" t="inlineStr">
         <is>
-          <t>7.545.532,00</t>
+          <t>640.693.958,00</t>
         </is>
       </c>
       <c r="O43" s="29" t="inlineStr">
         <is>
-          <t>6.340.783,00</t>
+          <t>538.398.284,00</t>
         </is>
       </c>
       <c r="P43" s="29" t="inlineStr">
@@ -5249,7 +6112,7 @@
       </c>
       <c r="Q43" s="29" t="inlineStr">
         <is>
-          <t>1.204.749,00</t>
+          <t>102.295.674,00</t>
         </is>
       </c>
       <c r="R43" s="29" t="inlineStr">
@@ -5307,31 +6170,39 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n"/>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>5314090802</t>
+          <t>5314209533</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>PMP1266993002</t>
+          <t>PMP1286466002</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>24-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G44" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H44" s="29" t="inlineStr">
         <is>
-          <t>4633161077</t>
+          <t>4634614433</t>
         </is>
       </c>
       <c r="I44" s="29" t="inlineStr">
@@ -5349,12 +6220,12 @@
       <c r="M44" s="29" t="n"/>
       <c r="N44" s="29" t="inlineStr">
         <is>
-          <t>-1.085.506,00</t>
+          <t>-4.623.481,00</t>
         </is>
       </c>
       <c r="O44" s="29" t="inlineStr">
         <is>
-          <t>-912.190,00</t>
+          <t>-3.885.278,00</t>
         </is>
       </c>
       <c r="P44" s="29" t="inlineStr">
@@ -5364,7 +6235,7 @@
       </c>
       <c r="Q44" s="29" t="inlineStr">
         <is>
-          <t>-173.316,00</t>
+          <t>-738.203,00</t>
         </is>
       </c>
       <c r="R44" s="29" t="inlineStr">
@@ -5422,31 +6293,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n"/>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C45" s="29" t="inlineStr">
         <is>
-          <t>5133526726</t>
+          <t>5134011789</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>PMP1267064001</t>
+          <t>PMP1286466CP001</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>17-09-2025</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G45" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>4633066523</t>
+          <t>4634614433</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
@@ -5464,12 +6343,12 @@
       <c r="M45" s="29" t="n"/>
       <c r="N45" s="29" t="inlineStr">
         <is>
-          <t>7.802.412,00</t>
+          <t>4.384.860,00</t>
         </is>
       </c>
       <c r="O45" s="29" t="inlineStr">
         <is>
-          <t>6.735.897,00</t>
+          <t>3.684.756,00</t>
         </is>
       </c>
       <c r="P45" s="29" t="inlineStr">
@@ -5479,7 +6358,7 @@
       </c>
       <c r="Q45" s="29" t="inlineStr">
         <is>
-          <t>1.066.515,00</t>
+          <t>700.104,00</t>
         </is>
       </c>
       <c r="R45" s="29" t="inlineStr">
@@ -5537,31 +6416,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n"/>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>5133720086</t>
+          <t>5133850409</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>PMP1267065001</t>
+          <t>PMP1286467001</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>12-09-2025</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G46" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G46" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H46" s="29" t="inlineStr">
         <is>
-          <t>4633143030</t>
+          <t>4634614433</t>
         </is>
       </c>
       <c r="I46" s="29" t="inlineStr">
@@ -5579,12 +6466,12 @@
       <c r="M46" s="29" t="n"/>
       <c r="N46" s="29" t="inlineStr">
         <is>
-          <t>32.139.462,00</t>
+          <t>137.894.507,00</t>
         </is>
       </c>
       <c r="O46" s="29" t="inlineStr">
         <is>
-          <t>27.746.296,00</t>
+          <t>115.877.737,00</t>
         </is>
       </c>
       <c r="P46" s="29" t="inlineStr">
@@ -5594,7 +6481,7 @@
       </c>
       <c r="Q46" s="29" t="inlineStr">
         <is>
-          <t>4.393.166,00</t>
+          <t>22.016.770,00</t>
         </is>
       </c>
       <c r="R46" s="29" t="inlineStr">
@@ -5649,34 +6536,42 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C47" s="29" t="inlineStr">
         <is>
-          <t>5314065044</t>
+          <t>5134025891</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>PMP1267065002</t>
+          <t>PMP1291552001</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G47" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H47" s="29" t="inlineStr">
         <is>
-          <t>4633143030</t>
+          <t>4634848035</t>
         </is>
       </c>
       <c r="I47" s="29" t="inlineStr">
@@ -5694,12 +6589,12 @@
       <c r="M47" s="29" t="n"/>
       <c r="N47" s="29" t="inlineStr">
         <is>
-          <t>-90,00</t>
+          <t>4.175.700,00</t>
         </is>
       </c>
       <c r="O47" s="29" t="inlineStr">
         <is>
-          <t>-76,00</t>
+          <t>3.508.992,00</t>
         </is>
       </c>
       <c r="P47" s="29" t="inlineStr">
@@ -5709,7 +6604,7 @@
       </c>
       <c r="Q47" s="29" t="inlineStr">
         <is>
-          <t>-14,00</t>
+          <t>666.708,00</t>
         </is>
       </c>
       <c r="R47" s="29" t="inlineStr">
@@ -5767,31 +6662,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C48" s="29" t="inlineStr">
         <is>
-          <t>5133632455</t>
+          <t>5134022794</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>PMP1267066001</t>
+          <t>PMP1291553001</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G48" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H48" s="29" t="inlineStr">
         <is>
-          <t>4633078468</t>
+          <t>4634848036</t>
         </is>
       </c>
       <c r="I48" s="29" t="inlineStr">
@@ -5809,12 +6712,12 @@
       <c r="M48" s="29" t="n"/>
       <c r="N48" s="29" t="inlineStr">
         <is>
-          <t>36.393.214,00</t>
+          <t>41.784.948,00</t>
         </is>
       </c>
       <c r="O48" s="29" t="inlineStr">
         <is>
-          <t>31.418.600,00</t>
+          <t>35.113.402,00</t>
         </is>
       </c>
       <c r="P48" s="29" t="inlineStr">
@@ -5824,7 +6727,7 @@
       </c>
       <c r="Q48" s="29" t="inlineStr">
         <is>
-          <t>4.974.614,00</t>
+          <t>6.671.546,00</t>
         </is>
       </c>
       <c r="R48" s="29" t="inlineStr">
@@ -5879,34 +6782,42 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C49" s="29" t="inlineStr">
         <is>
-          <t>5314112706</t>
+          <t>5134022796</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>PMP1267066002</t>
+          <t>PMP1291554001</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G49" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G49" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>4633078468</t>
+          <t>4633049196</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
@@ -5924,12 +6835,12 @@
       <c r="M49" s="29" t="n"/>
       <c r="N49" s="29" t="inlineStr">
         <is>
-          <t>-103,00</t>
+          <t>1.230.911,00</t>
         </is>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
-          <t>-87,00</t>
+          <t>1.034.379,00</t>
         </is>
       </c>
       <c r="P49" s="29" t="inlineStr">
@@ -5939,7 +6850,7 @@
       </c>
       <c r="Q49" s="29" t="inlineStr">
         <is>
-          <t>-16,00</t>
+          <t>196.532,00</t>
         </is>
       </c>
       <c r="R49" s="29" t="inlineStr">
@@ -5997,31 +6908,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n"/>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>5132757392</t>
+          <t>5133904611</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>PMP1267067001</t>
+          <t>PMP1291555001</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G50" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H50" s="29" t="inlineStr">
         <is>
-          <t>4633154180</t>
+          <t>4634645683</t>
         </is>
       </c>
       <c r="I50" s="29" t="inlineStr">
@@ -6039,12 +6958,12 @@
       <c r="M50" s="29" t="n"/>
       <c r="N50" s="29" t="inlineStr">
         <is>
-          <t>13.978.207,00</t>
+          <t>347.975,00</t>
         </is>
       </c>
       <c r="O50" s="29" t="inlineStr">
         <is>
-          <t>12.067.426,00</t>
+          <t>292.416,00</t>
         </is>
       </c>
       <c r="P50" s="29" t="inlineStr">
@@ -6054,7 +6973,7 @@
       </c>
       <c r="Q50" s="29" t="inlineStr">
         <is>
-          <t>1.910.781,00</t>
+          <t>55.559,00</t>
         </is>
       </c>
       <c r="R50" s="29" t="inlineStr">
@@ -6112,31 +7031,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n"/>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C51" s="29" t="inlineStr">
         <is>
-          <t>5133736935</t>
+          <t>5133989020</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>PMP1267068001</t>
+          <t>PMP1291556001</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G51" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H51" s="29" t="inlineStr">
         <is>
-          <t>4633186911</t>
+          <t>4634645685</t>
         </is>
       </c>
       <c r="I51" s="29" t="inlineStr">
@@ -6154,12 +7081,12 @@
       <c r="M51" s="29" t="n"/>
       <c r="N51" s="29" t="inlineStr">
         <is>
-          <t>10.918.828,00</t>
+          <t>47.200.683,00</t>
         </is>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
-          <t>9.175.485,00</t>
+          <t>39.664.440,00</t>
         </is>
       </c>
       <c r="P51" s="29" t="inlineStr">
@@ -6169,7 +7096,7 @@
       </c>
       <c r="Q51" s="29" t="inlineStr">
         <is>
-          <t>1.743.343,00</t>
+          <t>7.536.243,00</t>
         </is>
       </c>
       <c r="R51" s="29" t="inlineStr">
@@ -6224,34 +7151,42 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B52" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
-          <t>5314127753</t>
+          <t>5133874712</t>
         </is>
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>PMP1267068002</t>
+          <t>PMP1291557001</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>7701008009196</t>
-        </is>
-      </c>
-      <c r="G52" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G52" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H52" s="29" t="inlineStr">
         <is>
-          <t>4633186911</t>
+          <t>4633049193</t>
         </is>
       </c>
       <c r="I52" s="29" t="inlineStr">
@@ -6269,12 +7204,12 @@
       <c r="M52" s="29" t="n"/>
       <c r="N52" s="29" t="inlineStr">
         <is>
-          <t>-1.570.791,00</t>
+          <t>173.988,00</t>
         </is>
       </c>
       <c r="O52" s="29" t="inlineStr">
         <is>
-          <t>-1.319.992,00</t>
+          <t>146.208,00</t>
         </is>
       </c>
       <c r="P52" s="29" t="inlineStr">
@@ -6284,7 +7219,7 @@
       </c>
       <c r="Q52" s="29" t="inlineStr">
         <is>
-          <t>-250.799,00</t>
+          <t>27.780,00</t>
         </is>
       </c>
       <c r="R52" s="29" t="inlineStr">
@@ -6339,34 +7274,42 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="n"/>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C53" s="29" t="inlineStr">
         <is>
-          <t>5133661522</t>
+          <t>5314093216</t>
         </is>
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>PMP1267239001</t>
+          <t>PMP1291558001</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G53" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G53" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>4633046477</t>
+          <t>4633049194</t>
         </is>
       </c>
       <c r="I53" s="29" t="inlineStr">
@@ -6384,12 +7327,12 @@
       <c r="M53" s="29" t="n"/>
       <c r="N53" s="29" t="inlineStr">
         <is>
-          <t>24.772.082,00</t>
+          <t>-7,00</t>
         </is>
       </c>
       <c r="O53" s="29" t="inlineStr">
         <is>
-          <t>20.816.876,00</t>
+          <t>-6,00</t>
         </is>
       </c>
       <c r="P53" s="29" t="inlineStr">
@@ -6399,7 +7342,7 @@
       </c>
       <c r="Q53" s="29" t="inlineStr">
         <is>
-          <t>3.955.206,00</t>
+          <t>-1,00</t>
         </is>
       </c>
       <c r="R53" s="29" t="inlineStr">
@@ -6454,34 +7397,42 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="B54" s="29" t="n"/>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>5314078965</t>
+          <t>5134033901</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>PMP1267239002</t>
+          <t>PMP1291558002</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G54" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G54" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>4633046477</t>
+          <t>4633049194</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
@@ -6499,12 +7450,12 @@
       <c r="M54" s="29" t="n"/>
       <c r="N54" s="29" t="inlineStr">
         <is>
-          <t>-441.292,00</t>
+          <t>554.871,00</t>
         </is>
       </c>
       <c r="O54" s="29" t="inlineStr">
         <is>
-          <t>-370.834,00</t>
+          <t>466.278,00</t>
         </is>
       </c>
       <c r="P54" s="29" t="inlineStr">
@@ -6514,7 +7465,7 @@
       </c>
       <c r="Q54" s="29" t="inlineStr">
         <is>
-          <t>-70.458,00</t>
+          <t>88.593,00</t>
         </is>
       </c>
       <c r="R54" s="29" t="inlineStr">
@@ -6569,34 +7520,42 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="n"/>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C55" s="29" t="inlineStr">
         <is>
-          <t>5132153727</t>
+          <t>5314130005</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>PMP1267240001</t>
+          <t>PMP1291559001</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G55" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>4633074800</t>
+          <t>4633049199</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
@@ -6614,12 +7573,12 @@
       <c r="M55" s="29" t="n"/>
       <c r="N55" s="29" t="inlineStr">
         <is>
-          <t>47.305.349,00</t>
+          <t>-94.939,00</t>
         </is>
       </c>
       <c r="O55" s="29" t="inlineStr">
         <is>
-          <t>39.752.394,00</t>
+          <t>-79.781,00</t>
         </is>
       </c>
       <c r="P55" s="29" t="inlineStr">
@@ -6629,7 +7588,7 @@
       </c>
       <c r="Q55" s="29" t="inlineStr">
         <is>
-          <t>7.552.955,00</t>
+          <t>-15.158,00</t>
         </is>
       </c>
       <c r="R55" s="29" t="inlineStr">
@@ -6687,31 +7646,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n"/>
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>5132452731</t>
+          <t>5133796749</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>PMP1267241001</t>
+          <t>PMP1291559002</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G56" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G56" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>4633074800</t>
+          <t>4633049199</t>
         </is>
       </c>
       <c r="I56" s="29" t="inlineStr">
@@ -6729,12 +7696,12 @@
       <c r="M56" s="29" t="n"/>
       <c r="N56" s="29" t="inlineStr">
         <is>
-          <t>18.259.554,00</t>
+          <t>7.395.027,00</t>
         </is>
       </c>
       <c r="O56" s="29" t="inlineStr">
         <is>
-          <t>15.344.163,00</t>
+          <t>6.214.309,00</t>
         </is>
       </c>
       <c r="P56" s="29" t="inlineStr">
@@ -6744,7 +7711,7 @@
       </c>
       <c r="Q56" s="29" t="inlineStr">
         <is>
-          <t>2.915.391,00</t>
+          <t>1.180.718,00</t>
         </is>
       </c>
       <c r="R56" s="29" t="inlineStr">
@@ -6799,34 +7766,42 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="B57" s="29" t="n"/>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C57" s="29" t="inlineStr">
         <is>
-          <t>5133702220</t>
+          <t>5314175978</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>PMP1267242001</t>
+          <t>PMP1291560001</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G57" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G57" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H57" s="29" t="inlineStr">
         <is>
-          <t>4633074801</t>
+          <t>4634951004</t>
         </is>
       </c>
       <c r="I57" s="29" t="inlineStr">
@@ -6844,12 +7819,12 @@
       <c r="M57" s="29" t="n"/>
       <c r="N57" s="29" t="inlineStr">
         <is>
-          <t>2.037.042,00</t>
+          <t>-1.101,00</t>
         </is>
       </c>
       <c r="O57" s="29" t="inlineStr">
         <is>
-          <t>1.711.800,00</t>
+          <t>-925,00</t>
         </is>
       </c>
       <c r="P57" s="29" t="inlineStr">
@@ -6859,7 +7834,7 @@
       </c>
       <c r="Q57" s="29" t="inlineStr">
         <is>
-          <t>325.242,00</t>
+          <t>-176,00</t>
         </is>
       </c>
       <c r="R57" s="29" t="inlineStr">
@@ -6917,31 +7892,39 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n"/>
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>5133557628</t>
+          <t>5133955418</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>PMP1267243001</t>
+          <t>PMP1291560002</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G58" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H58" s="29" t="inlineStr">
         <is>
-          <t>4633074805</t>
+          <t>4634951004</t>
         </is>
       </c>
       <c r="I58" s="29" t="inlineStr">
@@ -6959,12 +7942,12 @@
       <c r="M58" s="29" t="n"/>
       <c r="N58" s="29" t="inlineStr">
         <is>
-          <t>18.134.888,00</t>
+          <t>62.932.311,00</t>
         </is>
       </c>
       <c r="O58" s="29" t="inlineStr">
         <is>
-          <t>15.239.401,00</t>
+          <t>52.884.295,00</t>
         </is>
       </c>
       <c r="P58" s="29" t="inlineStr">
@@ -6974,7 +7957,7 @@
       </c>
       <c r="Q58" s="29" t="inlineStr">
         <is>
-          <t>2.895.487,00</t>
+          <t>10.048.016,00</t>
         </is>
       </c>
       <c r="R58" s="29" t="inlineStr">
@@ -7032,31 +8015,39 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n"/>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
       <c r="C59" s="29" t="inlineStr">
         <is>
-          <t>5314117649</t>
+          <t>5314230579</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>PMP1267243002</t>
+          <t>PMP1291561001</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>25-07-2025</t>
+          <t>25-09-2025</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>7701008009455</t>
-        </is>
-      </c>
-      <c r="G59" s="29" t="n"/>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>4633074805</t>
+          <t>4633049195</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
@@ -7074,12 +8065,12 @@
       <c r="M59" s="29" t="n"/>
       <c r="N59" s="29" t="inlineStr">
         <is>
-          <t>-84.475,00</t>
+          <t>-869.290,00</t>
         </is>
       </c>
       <c r="O59" s="29" t="inlineStr">
         <is>
-          <t>-70.987,00</t>
+          <t>-730.496,00</t>
         </is>
       </c>
       <c r="P59" s="29" t="inlineStr">
@@ -7089,7 +8080,7 @@
       </c>
       <c r="Q59" s="29" t="inlineStr">
         <is>
-          <t>-13.488,00</t>
+          <t>-138.794,00</t>
         </is>
       </c>
       <c r="R59" s="29" t="inlineStr">
@@ -7142,87 +8133,3527 @@
       <c r="AC59" s="29" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>5134049763</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291561002</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>4633049195</t>
+        </is>
+      </c>
+      <c r="I60" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="n"/>
+      <c r="L60" s="29" t="n"/>
+      <c r="M60" s="29" t="n"/>
+      <c r="N60" s="29" t="inlineStr">
+        <is>
+          <t>43.153.227,00</t>
+        </is>
+      </c>
+      <c r="O60" s="29" t="inlineStr">
+        <is>
+          <t>36.263.216,00</t>
+        </is>
+      </c>
+      <c r="P60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q60" s="29" t="inlineStr">
+        <is>
+          <t>6.890.011,00</t>
+        </is>
+      </c>
+      <c r="R60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z60" s="29" t="n"/>
+      <c r="AA60" s="29" t="n"/>
+      <c r="AB60" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC60" s="29" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>5134052773</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291561CP001</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>29-09-2025</t>
+        </is>
+      </c>
+      <c r="F61" s="29" t="inlineStr">
+        <is>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G61" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H61" s="29" t="inlineStr">
+        <is>
+          <t>4633049195</t>
+        </is>
+      </c>
+      <c r="I61" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="n"/>
+      <c r="L61" s="29" t="n"/>
+      <c r="M61" s="29" t="n"/>
+      <c r="N61" s="29" t="inlineStr">
+        <is>
+          <t>869.400,00</t>
+        </is>
+      </c>
+      <c r="O61" s="29" t="inlineStr">
+        <is>
+          <t>730.588,00</t>
+        </is>
+      </c>
+      <c r="P61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q61" s="29" t="inlineStr">
+        <is>
+          <t>138.812,00</t>
+        </is>
+      </c>
+      <c r="R61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z61" s="29" t="n"/>
+      <c r="AA61" s="29" t="n"/>
+      <c r="AB61" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC61" s="29" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>5133972181</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291562001</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F62" s="29" t="inlineStr">
+        <is>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G62" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H62" s="29" t="inlineStr">
+        <is>
+          <t>4633049195</t>
+        </is>
+      </c>
+      <c r="I62" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n"/>
+      <c r="L62" s="29" t="n"/>
+      <c r="M62" s="29" t="n"/>
+      <c r="N62" s="29" t="inlineStr">
+        <is>
+          <t>7.043.900,00</t>
+        </is>
+      </c>
+      <c r="O62" s="29" t="inlineStr">
+        <is>
+          <t>5.919.244,00</t>
+        </is>
+      </c>
+      <c r="P62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q62" s="29" t="inlineStr">
+        <is>
+          <t>1.124.656,00</t>
+        </is>
+      </c>
+      <c r="R62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z62" s="29" t="n"/>
+      <c r="AA62" s="29" t="n"/>
+      <c r="AB62" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC62" s="29" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>3208958564</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291563001</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H63" s="29" t="n"/>
+      <c r="I63" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="n"/>
+      <c r="L63" s="29" t="n"/>
+      <c r="M63" s="29" t="n"/>
+      <c r="N63" s="29" t="inlineStr">
+        <is>
+          <t>-8.705,00</t>
+        </is>
+      </c>
+      <c r="O63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="P63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="R63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z63" s="29" t="n"/>
+      <c r="AA63" s="29" t="n"/>
+      <c r="AB63" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC63" s="29" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>5133972159</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291563002</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F64" s="29" t="inlineStr">
+        <is>
+          <t>7701008109001</t>
+        </is>
+      </c>
+      <c r="G64" s="29" t="inlineStr">
+        <is>
+          <t>CD 900 BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H64" s="29" t="inlineStr">
+        <is>
+          <t>4634645692</t>
+        </is>
+      </c>
+      <c r="I64" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K64" s="29" t="n"/>
+      <c r="L64" s="29" t="n"/>
+      <c r="M64" s="29" t="n"/>
+      <c r="N64" s="29" t="inlineStr">
+        <is>
+          <t>82.462.892,00</t>
+        </is>
+      </c>
+      <c r="O64" s="29" t="inlineStr">
+        <is>
+          <t>69.296.548,00</t>
+        </is>
+      </c>
+      <c r="P64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q64" s="29" t="inlineStr">
+        <is>
+          <t>13.166.344,00</t>
+        </is>
+      </c>
+      <c r="R64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z64" s="29" t="n"/>
+      <c r="AA64" s="29" t="n"/>
+      <c r="AB64" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC64" s="29" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>5133392594</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291965001</t>
+        </is>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F65" s="29" t="inlineStr">
+        <is>
+          <t>7701008009493</t>
+        </is>
+      </c>
+      <c r="G65" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro de Distribución CD 8033 Víveres </t>
+        </is>
+      </c>
+      <c r="H65" s="29" t="inlineStr">
+        <is>
+          <t>4634972068</t>
+        </is>
+      </c>
+      <c r="I65" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" s="29" t="n"/>
+      <c r="L65" s="29" t="n"/>
+      <c r="M65" s="29" t="n"/>
+      <c r="N65" s="29" t="inlineStr">
+        <is>
+          <t>7.349.759,00</t>
+        </is>
+      </c>
+      <c r="O65" s="29" t="inlineStr">
+        <is>
+          <t>6.176.268,00</t>
+        </is>
+      </c>
+      <c r="P65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q65" s="29" t="inlineStr">
+        <is>
+          <t>1.173.491,00</t>
+        </is>
+      </c>
+      <c r="R65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z65" s="29" t="n"/>
+      <c r="AA65" s="29" t="n"/>
+      <c r="AB65" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC65" s="29" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>5313850904</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>PMP1291965002</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>25-09-2025</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>7701008009493</t>
+        </is>
+      </c>
+      <c r="G66" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro de Distribución CD 8033 Víveres </t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>4634972068</t>
+        </is>
+      </c>
+      <c r="I66" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K66" s="29" t="n"/>
+      <c r="L66" s="29" t="n"/>
+      <c r="M66" s="29" t="n"/>
+      <c r="N66" s="29" t="inlineStr">
+        <is>
+          <t>-153.246,00</t>
+        </is>
+      </c>
+      <c r="O66" s="29" t="inlineStr">
+        <is>
+          <t>-128.778,00</t>
+        </is>
+      </c>
+      <c r="P66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q66" s="29" t="inlineStr">
+        <is>
+          <t>-24.468,00</t>
+        </is>
+      </c>
+      <c r="R66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z66" s="29" t="n"/>
+      <c r="AA66" s="29" t="n"/>
+      <c r="AB66" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC66" s="29" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>5134048792</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292294001</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F67" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G67" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>4634848039</t>
+        </is>
+      </c>
+      <c r="I67" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J67" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K67" s="29" t="n"/>
+      <c r="L67" s="29" t="n"/>
+      <c r="M67" s="29" t="n"/>
+      <c r="N67" s="29" t="inlineStr">
+        <is>
+          <t>3.131.775,00</t>
+        </is>
+      </c>
+      <c r="O67" s="29" t="inlineStr">
+        <is>
+          <t>2.631.744,00</t>
+        </is>
+      </c>
+      <c r="P67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q67" s="29" t="inlineStr">
+        <is>
+          <t>500.031,00</t>
+        </is>
+      </c>
+      <c r="R67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z67" s="29" t="n"/>
+      <c r="AA67" s="29" t="n"/>
+      <c r="AB67" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC67" s="29" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>5134008025</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292295001</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>4634786139</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="n"/>
+      <c r="L68" s="29" t="n"/>
+      <c r="M68" s="29" t="n"/>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>86.994,00</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>73.104,00</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>13.890,00</t>
+        </is>
+      </c>
+      <c r="R68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z68" s="29" t="n"/>
+      <c r="AA68" s="29" t="n"/>
+      <c r="AB68" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC68" s="29" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>5133929235</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292296001</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>4634786141</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="n"/>
+      <c r="L69" s="29" t="n"/>
+      <c r="M69" s="29" t="n"/>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>13.811.678,00</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>11.606.452,00</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>2.205.226,00</t>
+        </is>
+      </c>
+      <c r="R69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z69" s="29" t="n"/>
+      <c r="AA69" s="29" t="n"/>
+      <c r="AB69" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC69" s="29" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>5133991956</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292297001</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>4634786147</t>
+        </is>
+      </c>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="n"/>
+      <c r="L70" s="29" t="n"/>
+      <c r="M70" s="29" t="n"/>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>32.030.709,00</t>
+        </is>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>26.916.562,00</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q70" s="29" t="inlineStr">
+        <is>
+          <t>5.114.147,00</t>
+        </is>
+      </c>
+      <c r="R70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z70" s="29" t="n"/>
+      <c r="AA70" s="29" t="n"/>
+      <c r="AB70" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC70" s="29" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>5134048782</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292298001</t>
+        </is>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>4634947902</t>
+        </is>
+      </c>
+      <c r="I71" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J71" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" s="29" t="n"/>
+      <c r="L71" s="29" t="n"/>
+      <c r="M71" s="29" t="n"/>
+      <c r="N71" s="29" t="inlineStr">
+        <is>
+          <t>34.758.235,00</t>
+        </is>
+      </c>
+      <c r="O71" s="29" t="inlineStr">
+        <is>
+          <t>29.208.601,00</t>
+        </is>
+      </c>
+      <c r="P71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q71" s="29" t="inlineStr">
+        <is>
+          <t>5.549.634,00</t>
+        </is>
+      </c>
+      <c r="R71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z71" s="29" t="n"/>
+      <c r="AA71" s="29" t="n"/>
+      <c r="AB71" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC71" s="29" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B72" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>5314118000</t>
+        </is>
+      </c>
+      <c r="D72" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292298002</t>
+        </is>
+      </c>
+      <c r="E72" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F72" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G72" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H72" s="29" t="inlineStr">
+        <is>
+          <t>4634947902</t>
+        </is>
+      </c>
+      <c r="I72" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J72" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K72" s="29" t="n"/>
+      <c r="L72" s="29" t="n"/>
+      <c r="M72" s="29" t="n"/>
+      <c r="N72" s="29" t="inlineStr">
+        <is>
+          <t>-608,00</t>
+        </is>
+      </c>
+      <c r="O72" s="29" t="inlineStr">
+        <is>
+          <t>-511,00</t>
+        </is>
+      </c>
+      <c r="P72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q72" s="29" t="inlineStr">
+        <is>
+          <t>-97,00</t>
+        </is>
+      </c>
+      <c r="R72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z72" s="29" t="n"/>
+      <c r="AA72" s="29" t="n"/>
+      <c r="AB72" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC72" s="29" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>5134049788</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292309001</t>
+        </is>
+      </c>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F73" s="29" t="inlineStr">
+        <is>
+          <t>7701008009455</t>
+        </is>
+      </c>
+      <c r="G73" s="29" t="inlineStr">
+        <is>
+          <t>CD 945 VIVERES CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>4634848040</t>
+        </is>
+      </c>
+      <c r="I73" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J73" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K73" s="29" t="n"/>
+      <c r="L73" s="29" t="n"/>
+      <c r="M73" s="29" t="n"/>
+      <c r="N73" s="29" t="inlineStr">
+        <is>
+          <t>20.376.766,00</t>
+        </is>
+      </c>
+      <c r="O73" s="29" t="inlineStr">
+        <is>
+          <t>17.123.333,00</t>
+        </is>
+      </c>
+      <c r="P73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q73" s="29" t="inlineStr">
+        <is>
+          <t>3.253.433,00</t>
+        </is>
+      </c>
+      <c r="R73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z73" s="29" t="n"/>
+      <c r="AA73" s="29" t="n"/>
+      <c r="AB73" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC73" s="29" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>5134027908</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292593001</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>4634764383</t>
+        </is>
+      </c>
+      <c r="I74" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J74" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K74" s="29" t="n"/>
+      <c r="L74" s="29" t="n"/>
+      <c r="M74" s="29" t="n"/>
+      <c r="N74" s="29" t="inlineStr">
+        <is>
+          <t>3.131.775,00</t>
+        </is>
+      </c>
+      <c r="O74" s="29" t="inlineStr">
+        <is>
+          <t>2.631.744,00</t>
+        </is>
+      </c>
+      <c r="P74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q74" s="29" t="inlineStr">
+        <is>
+          <t>500.031,00</t>
+        </is>
+      </c>
+      <c r="R74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z74" s="29" t="n"/>
+      <c r="AA74" s="29" t="n"/>
+      <c r="AB74" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC74" s="29" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B75" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>5134015962</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292594001</t>
+        </is>
+      </c>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F75" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G75" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>4634848037</t>
+        </is>
+      </c>
+      <c r="I75" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J75" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K75" s="29" t="n"/>
+      <c r="L75" s="29" t="n"/>
+      <c r="M75" s="29" t="n"/>
+      <c r="N75" s="29" t="inlineStr">
+        <is>
+          <t>30.380.462,00</t>
+        </is>
+      </c>
+      <c r="O75" s="29" t="inlineStr">
+        <is>
+          <t>25.529.800,00</t>
+        </is>
+      </c>
+      <c r="P75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q75" s="29" t="inlineStr">
+        <is>
+          <t>4.850.662,00</t>
+        </is>
+      </c>
+      <c r="R75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z75" s="29" t="n"/>
+      <c r="AA75" s="29" t="n"/>
+      <c r="AB75" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC75" s="29" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>5314156829</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292652001</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>4634731836</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="n"/>
+      <c r="L76" s="29" t="n"/>
+      <c r="M76" s="29" t="n"/>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>-143,00</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>-120,00</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>-23,00</t>
+        </is>
+      </c>
+      <c r="R76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z76" s="29" t="n"/>
+      <c r="AA76" s="29" t="n"/>
+      <c r="AB76" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC76" s="29" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>5133857657</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292652002</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>4634731836</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="n"/>
+      <c r="L77" s="29" t="n"/>
+      <c r="M77" s="29" t="n"/>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>30.145.687,00</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>25.332.510,00</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>4.813.177,00</t>
+        </is>
+      </c>
+      <c r="R77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z77" s="29" t="n"/>
+      <c r="AA77" s="29" t="n"/>
+      <c r="AB77" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC77" s="29" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>5134008032</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292653001</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>4634731841</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J78" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" s="29" t="n"/>
+      <c r="L78" s="29" t="n"/>
+      <c r="M78" s="29" t="n"/>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>27.925.239,00</t>
+        </is>
+      </c>
+      <c r="O78" s="29" t="inlineStr">
+        <is>
+          <t>23.466.587,00</t>
+        </is>
+      </c>
+      <c r="P78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q78" s="29" t="inlineStr">
+        <is>
+          <t>4.458.652,00</t>
+        </is>
+      </c>
+      <c r="R78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z78" s="29" t="n"/>
+      <c r="AA78" s="29" t="n"/>
+      <c r="AB78" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC78" s="29" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>5133969309</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292654001</t>
+        </is>
+      </c>
+      <c r="E79" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F79" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G79" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H79" s="29" t="inlineStr">
+        <is>
+          <t>4634951005</t>
+        </is>
+      </c>
+      <c r="I79" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J79" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K79" s="29" t="n"/>
+      <c r="L79" s="29" t="n"/>
+      <c r="M79" s="29" t="n"/>
+      <c r="N79" s="29" t="inlineStr">
+        <is>
+          <t>46.242.233,00</t>
+        </is>
+      </c>
+      <c r="O79" s="29" t="inlineStr">
+        <is>
+          <t>38.859.019,00</t>
+        </is>
+      </c>
+      <c r="P79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q79" s="29" t="inlineStr">
+        <is>
+          <t>7.383.214,00</t>
+        </is>
+      </c>
+      <c r="R79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z79" s="29" t="n"/>
+      <c r="AA79" s="29" t="n"/>
+      <c r="AB79" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC79" s="29" t="n"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>5314122356</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292654002</t>
+        </is>
+      </c>
+      <c r="E80" s="29" t="inlineStr">
+        <is>
+          <t>26-09-2025</t>
+        </is>
+      </c>
+      <c r="F80" s="29" t="inlineStr">
+        <is>
+          <t>7701008009196</t>
+        </is>
+      </c>
+      <c r="G80" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 919 VIVERES BOGOTA              </t>
+        </is>
+      </c>
+      <c r="H80" s="29" t="inlineStr">
+        <is>
+          <t>4634951005</t>
+        </is>
+      </c>
+      <c r="I80" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J80" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K80" s="29" t="n"/>
+      <c r="L80" s="29" t="n"/>
+      <c r="M80" s="29" t="n"/>
+      <c r="N80" s="29" t="inlineStr">
+        <is>
+          <t>-808,00</t>
+        </is>
+      </c>
+      <c r="O80" s="29" t="inlineStr">
+        <is>
+          <t>-679,00</t>
+        </is>
+      </c>
+      <c r="P80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q80" s="29" t="inlineStr">
+        <is>
+          <t>-129,00</t>
+        </is>
+      </c>
+      <c r="R80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z80" s="29" t="n"/>
+      <c r="AA80" s="29" t="n"/>
+      <c r="AB80" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC80" s="29" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>5133911574</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292704001</t>
+        </is>
+      </c>
+      <c r="E81" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F81" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G81" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H81" s="29" t="inlineStr">
+        <is>
+          <t>4634848038</t>
+        </is>
+      </c>
+      <c r="I81" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J81" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K81" s="29" t="n"/>
+      <c r="L81" s="29" t="n"/>
+      <c r="M81" s="29" t="n"/>
+      <c r="N81" s="29" t="inlineStr">
+        <is>
+          <t>4.192.185,00</t>
+        </is>
+      </c>
+      <c r="O81" s="29" t="inlineStr">
+        <is>
+          <t>3.522.845,00</t>
+        </is>
+      </c>
+      <c r="P81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q81" s="29" t="inlineStr">
+        <is>
+          <t>669.340,00</t>
+        </is>
+      </c>
+      <c r="R81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z81" s="29" t="n"/>
+      <c r="AA81" s="29" t="n"/>
+      <c r="AB81" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC81" s="29" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>5133897546</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292712001</t>
+        </is>
+      </c>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F82" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G82" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H82" s="29" t="inlineStr">
+        <is>
+          <t>4634725029</t>
+        </is>
+      </c>
+      <c r="I82" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J82" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K82" s="29" t="n"/>
+      <c r="L82" s="29" t="n"/>
+      <c r="M82" s="29" t="n"/>
+      <c r="N82" s="29" t="inlineStr">
+        <is>
+          <t>16.403.804,00</t>
+        </is>
+      </c>
+      <c r="O82" s="29" t="inlineStr">
+        <is>
+          <t>13.784.709,00</t>
+        </is>
+      </c>
+      <c r="P82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q82" s="29" t="inlineStr">
+        <is>
+          <t>2.619.095,00</t>
+        </is>
+      </c>
+      <c r="R82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z82" s="29" t="n"/>
+      <c r="AA82" s="29" t="n"/>
+      <c r="AB82" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC82" s="29" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>5314211611</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292712002</t>
+        </is>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F83" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G83" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H83" s="29" t="inlineStr">
+        <is>
+          <t>4634725029</t>
+        </is>
+      </c>
+      <c r="I83" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J83" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K83" s="29" t="n"/>
+      <c r="L83" s="29" t="n"/>
+      <c r="M83" s="29" t="n"/>
+      <c r="N83" s="29" t="inlineStr">
+        <is>
+          <t>-68,00</t>
+        </is>
+      </c>
+      <c r="O83" s="29" t="inlineStr">
+        <is>
+          <t>-57,00</t>
+        </is>
+      </c>
+      <c r="P83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q83" s="29" t="inlineStr">
+        <is>
+          <t>-11,00</t>
+        </is>
+      </c>
+      <c r="R83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z83" s="29" t="n"/>
+      <c r="AA83" s="29" t="n"/>
+      <c r="AB83" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC83" s="29" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B84" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>5133964027</t>
+        </is>
+      </c>
+      <c r="D84" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292713001</t>
+        </is>
+      </c>
+      <c r="E84" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F84" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G84" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H84" s="29" t="inlineStr">
+        <is>
+          <t>4634725033</t>
+        </is>
+      </c>
+      <c r="I84" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K84" s="29" t="n"/>
+      <c r="L84" s="29" t="n"/>
+      <c r="M84" s="29" t="n"/>
+      <c r="N84" s="29" t="inlineStr">
+        <is>
+          <t>31.007.952,00</t>
+        </is>
+      </c>
+      <c r="O84" s="29" t="inlineStr">
+        <is>
+          <t>26.057.103,00</t>
+        </is>
+      </c>
+      <c r="P84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q84" s="29" t="inlineStr">
+        <is>
+          <t>4.950.849,00</t>
+        </is>
+      </c>
+      <c r="R84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z84" s="29" t="n"/>
+      <c r="AA84" s="29" t="n"/>
+      <c r="AB84" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC84" s="29" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>5314219552</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292713002</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F85" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G85" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H85" s="29" t="inlineStr">
+        <is>
+          <t>4634725033</t>
+        </is>
+      </c>
+      <c r="I85" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J85" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K85" s="29" t="n"/>
+      <c r="L85" s="29" t="n"/>
+      <c r="M85" s="29" t="n"/>
+      <c r="N85" s="29" t="inlineStr">
+        <is>
+          <t>-9,00</t>
+        </is>
+      </c>
+      <c r="O85" s="29" t="inlineStr">
+        <is>
+          <t>-8,00</t>
+        </is>
+      </c>
+      <c r="P85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q85" s="29" t="inlineStr">
+        <is>
+          <t>-1,00</t>
+        </is>
+      </c>
+      <c r="R85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z85" s="29" t="n"/>
+      <c r="AA85" s="29" t="n"/>
+      <c r="AB85" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC85" s="29" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B86" s="29" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>5133954586</t>
+        </is>
+      </c>
+      <c r="D86" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292714001</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F86" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G86" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H86" s="29" t="inlineStr">
+        <is>
+          <t>4634947901</t>
+        </is>
+      </c>
+      <c r="I86" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K86" s="29" t="n"/>
+      <c r="L86" s="29" t="n"/>
+      <c r="M86" s="29" t="n"/>
+      <c r="N86" s="29" t="inlineStr">
+        <is>
+          <t>32.461.435,00</t>
+        </is>
+      </c>
+      <c r="O86" s="29" t="inlineStr">
+        <is>
+          <t>27.278.517,00</t>
+        </is>
+      </c>
+      <c r="P86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q86" s="29" t="inlineStr">
+        <is>
+          <t>5.182.918,00</t>
+        </is>
+      </c>
+      <c r="R86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z86" s="29" t="n"/>
+      <c r="AA86" s="29" t="n"/>
+      <c r="AB86" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC86" s="29" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>5314236511</t>
+        </is>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>PMP1292714002</t>
+        </is>
+      </c>
+      <c r="E87" s="29" t="inlineStr">
+        <is>
+          <t>27-09-2025</t>
+        </is>
+      </c>
+      <c r="F87" s="29" t="inlineStr">
+        <is>
+          <t>7701008009608</t>
+        </is>
+      </c>
+      <c r="G87" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD 960 VIVERES CALI                            </t>
+        </is>
+      </c>
+      <c r="H87" s="29" t="inlineStr">
+        <is>
+          <t>4634947901</t>
+        </is>
+      </c>
+      <c r="I87" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J87" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K87" s="29" t="n"/>
+      <c r="L87" s="29" t="n"/>
+      <c r="M87" s="29" t="n"/>
+      <c r="N87" s="29" t="inlineStr">
+        <is>
+          <t>-567,00</t>
+        </is>
+      </c>
+      <c r="O87" s="29" t="inlineStr">
+        <is>
+          <t>-477,00</t>
+        </is>
+      </c>
+      <c r="P87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q87" s="29" t="inlineStr">
+        <is>
+          <t>-90,00</t>
+        </is>
+      </c>
+      <c r="R87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="U87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z87" s="29" t="n"/>
+      <c r="AA87" s="29" t="n"/>
+      <c r="AB87" s="29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="AC87" s="29" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>Totales:</t>
         </is>
       </c>
-      <c r="B60" s="30" t="n"/>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="30" t="n"/>
-      <c r="E60" s="30" t="n"/>
-      <c r="F60" s="30" t="n"/>
-      <c r="G60" s="30" t="n"/>
-      <c r="H60" s="30" t="n"/>
-      <c r="I60" s="30" t="n"/>
-      <c r="J60" s="30" t="n"/>
-      <c r="K60" s="30" t="n"/>
-      <c r="L60" s="30" t="n"/>
-      <c r="M60" s="30" t="n"/>
-      <c r="N60" s="30" t="inlineStr">
-        <is>
-          <t>115.338.833,00</t>
-        </is>
-      </c>
-      <c r="O60" s="30" t="inlineStr">
-        <is>
-          <t>76.681.079,00</t>
-        </is>
-      </c>
-      <c r="P60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="Q60" s="30" t="inlineStr">
-        <is>
-          <t>29.588.698,00</t>
-        </is>
-      </c>
-      <c r="R60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="S60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="T60" s="30" t="inlineStr">
-        <is>
-          <t>9.069.056,00</t>
-        </is>
-      </c>
-      <c r="U60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="V60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="W60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="X60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="Y60" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="Z60" s="30" t="n"/>
-      <c r="AA60" s="30" t="n"/>
-      <c r="AB60" s="30" t="n"/>
-      <c r="AC60" s="30" t="n"/>
+      <c r="B88" s="30" t="n"/>
+      <c r="C88" s="30" t="n"/>
+      <c r="D88" s="30" t="n"/>
+      <c r="E88" s="30" t="n"/>
+      <c r="F88" s="30" t="n"/>
+      <c r="G88" s="30" t="n"/>
+      <c r="H88" s="30" t="n"/>
+      <c r="I88" s="30" t="n"/>
+      <c r="J88" s="30" t="n"/>
+      <c r="K88" s="30" t="n"/>
+      <c r="L88" s="30" t="n"/>
+      <c r="M88" s="30" t="n"/>
+      <c r="N88" s="30" t="inlineStr">
+        <is>
+          <t>2.007.111.196,00</t>
+        </is>
+      </c>
+      <c r="O88" s="30" t="inlineStr">
+        <is>
+          <t>1.691.500.570,00</t>
+        </is>
+      </c>
+      <c r="P88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q88" s="30" t="inlineStr">
+        <is>
+          <t>302.815.537,00</t>
+        </is>
+      </c>
+      <c r="R88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="S88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="T88" s="30" t="inlineStr">
+        <is>
+          <t>12.803.794,00</t>
+        </is>
+      </c>
+      <c r="U88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="V88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="W88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="X88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Y88" s="30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Z88" s="30" t="n"/>
+      <c r="AA88" s="30" t="n"/>
+      <c r="AB88" s="30" t="n"/>
+      <c r="AC88" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1254,16 +1254,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1286467</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>640693961.84</v>
+        <v>137894507.16</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>640693961.84</v>
+        <v>137894507.16</v>
       </c>
       <c r="I33" s="11" t="inlineStr"/>
     </row>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PMP1286467</t>
+          <t>PMP1291552</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>137894507.16</v>
+        <v>4175700</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>137894507.16</v>
+        <v>4175700</v>
       </c>
       <c r="I34" s="11" t="inlineStr"/>
     </row>
@@ -1296,16 +1296,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>PMP1291552</t>
+          <t>PMP1291553</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4175700</v>
+        <v>41784946.6</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>4175700</v>
+        <v>41784946.6</v>
       </c>
       <c r="I35" s="11" t="inlineStr"/>
     </row>
@@ -1317,16 +1317,16 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>PMP1291553</t>
+          <t>PMP1291554</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>41784946.6</v>
+        <v>1230911.12</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>41784946.6</v>
+        <v>1230911.12</v>
       </c>
       <c r="I36" s="11" t="inlineStr"/>
     </row>
@@ -1338,16 +1338,16 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PMP1291554</t>
+          <t>PMP1291555</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1230911.12</v>
+        <v>347975</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>1230911.12</v>
+        <v>347975</v>
       </c>
       <c r="I37" s="11" t="inlineStr"/>
     </row>
@@ -1359,16 +1359,16 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>PMP1291555</t>
+          <t>PMP1291556</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>347975</v>
+        <v>47200684.8</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>347975</v>
+        <v>47200684.8</v>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
     </row>
@@ -1380,16 +1380,16 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMP1291556</t>
+          <t>PMP1291557</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>47200684.8</v>
+        <v>173988</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>47200684.8</v>
+        <v>173988</v>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
     </row>
@@ -1401,16 +1401,16 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>PMP1291557</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>173988</v>
+        <v>554871.24</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>173988</v>
+        <v>554871.24</v>
       </c>
       <c r="I40" s="11" t="inlineStr"/>
     </row>
@@ -1422,16 +1422,16 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>PMP1291558</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>554871.24</v>
+        <v>7395026.5</v>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>554871.24</v>
+        <v>7395026.5</v>
       </c>
       <c r="I41" s="11" t="inlineStr"/>
     </row>
@@ -1443,16 +1443,16 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>PMP1291559</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7395026.5</v>
+        <v>62932310.75</v>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>7395026.5</v>
+        <v>62932310.75</v>
       </c>
       <c r="I42" s="11" t="inlineStr"/>
     </row>
@@ -1464,16 +1464,16 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PMP1291560</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>62932310.75</v>
+        <v>43153234.4</v>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
       <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>62932310.75</v>
+        <v>43153234.4</v>
       </c>
       <c r="I43" s="11" t="inlineStr"/>
     </row>
@@ -1485,16 +1485,16 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291562</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>43153234.4</v>
+        <v>7043898.34</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>43153234.4</v>
+        <v>7043898.34</v>
       </c>
       <c r="I44" s="11" t="inlineStr"/>
     </row>
@@ -1506,16 +1506,16 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>43153234.4</v>
+        <v>82462889.81999999</v>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr"/>
       <c r="H45" s="6" t="n">
-        <v>43153234.4</v>
+        <v>82462889.81999999</v>
       </c>
       <c r="I45" s="11" t="inlineStr"/>
     </row>
@@ -1527,16 +1527,16 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>PMP1291562</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7043898.34</v>
+        <v>7349759</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>7043898.34</v>
+        <v>7349759</v>
       </c>
       <c r="I46" s="11" t="inlineStr"/>
     </row>
@@ -1548,16 +1548,16 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PMP1291563</t>
+          <t>PMP1292294</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>82462889.81999999</v>
+        <v>3131775</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>82462889.81999999</v>
+        <v>3131775</v>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
     </row>
@@ -1569,16 +1569,16 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>PMP1291965</t>
+          <t>PMP1292295</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>7349759</v>
+        <v>86994</v>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="6" t="n">
-        <v>7349759</v>
+        <v>86994</v>
       </c>
       <c r="I48" s="11" t="inlineStr"/>
     </row>
@@ -1590,16 +1590,16 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>PMP1292294</t>
+          <t>PMP1292296</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>3131775</v>
+        <v>13811678.4</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>3131775</v>
+        <v>13811678.4</v>
       </c>
       <c r="I49" s="11" t="inlineStr"/>
     </row>
@@ -1611,16 +1611,16 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>PMP1292295</t>
+          <t>PMP1292297</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>86994</v>
+        <v>32030709.54</v>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr"/>
       <c r="H50" s="6" t="n">
-        <v>86994</v>
+        <v>32030709.54</v>
       </c>
       <c r="I50" s="11" t="inlineStr"/>
     </row>
@@ -1632,16 +1632,16 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>PMP1292296</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>13811678.4</v>
+        <v>34758234.75</v>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="6" t="n">
-        <v>13811678.4</v>
+        <v>34758234.75</v>
       </c>
       <c r="I51" s="11" t="inlineStr"/>
     </row>
@@ -1653,16 +1653,16 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>PMP1292297</t>
+          <t>PMP1292309</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>32030709.54</v>
+        <v>20376764.8</v>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
       <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="6" t="n">
-        <v>32030709.54</v>
+        <v>20376764.8</v>
       </c>
       <c r="I52" s="11" t="inlineStr"/>
     </row>
@@ -1674,16 +1674,16 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>PMP1292298</t>
+          <t>PMP1292593</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>34758234.75</v>
+        <v>3131775</v>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="6" t="n">
-        <v>34758234.75</v>
+        <v>3131775</v>
       </c>
       <c r="I53" s="11" t="inlineStr"/>
     </row>
@@ -1695,16 +1695,16 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>PMP1292309</t>
+          <t>PMP1292594</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>20376764.8</v>
+        <v>30380459.6</v>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
       <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="6" t="n">
-        <v>20376764.8</v>
+        <v>30380459.6</v>
       </c>
       <c r="I54" s="11" t="inlineStr"/>
     </row>
@@ -1716,16 +1716,16 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>PMP1292593</t>
+          <t>PMP1292652</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>3131775</v>
+        <v>30145687</v>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="6" t="n">
-        <v>3131775</v>
+        <v>30145687</v>
       </c>
       <c r="I55" s="11" t="inlineStr"/>
     </row>
@@ -1737,16 +1737,16 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>PMP1292594</t>
+          <t>PMP1292653</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>30380459.6</v>
+        <v>27925238.47</v>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
       <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="6" t="n">
-        <v>30380459.6</v>
+        <v>27925238.47</v>
       </c>
       <c r="I56" s="11" t="inlineStr"/>
     </row>
@@ -1758,16 +1758,16 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>PMP1292652</t>
+          <t>PMP1292654</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>30145687</v>
+        <v>46242233.5</v>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
       <c r="G57" s="10" t="inlineStr"/>
       <c r="H57" s="6" t="n">
-        <v>30145687</v>
+        <v>46242233.5</v>
       </c>
       <c r="I57" s="11" t="inlineStr"/>
     </row>
@@ -1779,16 +1779,16 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>PMP1292653</t>
+          <t>PMP1292704</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>27925238.47</v>
+        <v>4192184.8</v>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr"/>
       <c r="H58" s="6" t="n">
-        <v>27925238.47</v>
+        <v>4192184.8</v>
       </c>
       <c r="I58" s="11" t="inlineStr"/>
     </row>
@@ -1800,16 +1800,16 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>PMP1292654</t>
+          <t>PMP1292712</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>46242233.5</v>
+        <v>16403804</v>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
       <c r="G59" s="10" t="inlineStr"/>
       <c r="H59" s="6" t="n">
-        <v>46242233.5</v>
+        <v>16403804</v>
       </c>
       <c r="I59" s="11" t="inlineStr"/>
     </row>
@@ -1821,16 +1821,16 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>PMP1292704</t>
+          <t>PMP1292713</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>4192184.8</v>
+        <v>31007952.84</v>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="6" t="n">
-        <v>4192184.8</v>
+        <v>31007952.84</v>
       </c>
       <c r="I60" s="11" t="inlineStr"/>
     </row>
@@ -1842,60 +1842,84 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>PMP1292712</t>
+          <t>PMP1292714</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>16403804</v>
+        <v>32461435</v>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
       <c r="G61" s="10" t="inlineStr"/>
       <c r="H61" s="6" t="n">
-        <v>16403804</v>
+        <v>32461435</v>
       </c>
       <c r="I61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>PMP1292713</t>
+          <t>4636412647</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>31007952.84</v>
-      </c>
-      <c r="F62" s="10" t="inlineStr"/>
-      <c r="G62" s="10" t="inlineStr"/>
+        <v>-16320</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H62" s="6" t="n">
-        <v>31007952.84</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr"/>
+        <v>-16320</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>AVERIA 4636412647</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>PMP1292714</t>
+          <t>0085501420</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>32461435</v>
-      </c>
-      <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr"/>
+        <v>-11077235</v>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
       <c r="H63" s="6" t="n">
-        <v>32461435</v>
-      </c>
-      <c r="I63" s="11" t="inlineStr"/>
+        <v>-11077235</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>DESCUENTO 0085501420</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
@@ -1905,28 +1929,28 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>4636412647</t>
+          <t>9801673296</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-16320</v>
+        <v>-116500000</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>FACT PROVEEDOR</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>-16320</v>
+        <v>-116500000</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4636412647</t>
+          <t>FACT PROVEEDOR 9801673296</t>
         </is>
       </c>
     </row>
@@ -1938,94 +1962,94 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>0085501420</t>
+          <t>9801673633</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>-11077235</v>
+        <v>-296234085</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>FACT PROVEEDOR</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>-11077235</v>
+        <v>-296234085</v>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>DESCUENTO 0085501420</t>
+          <t>FACT PROVEEDOR 9801673633</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>9801673296</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-116500000</v>
+        <v>-70.07999997888692</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>-116500000</v>
+        <v>-70.07999997888692</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673296</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>9801673633</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>-296234085</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>-296234085</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673633</t>
+          <t>Myr Vlr Pagado PMP1286466</t>
         </is>
       </c>
     </row>
@@ -2037,94 +2061,94 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>-81.3200000107754</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>-81.3200000107754</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Myr Vlr Pagado PMP1291561</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1286182</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>-636309101.84</v>
+        <v>-232158</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>-636309101.84</v>
+        <v>-232158</v>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286466</t>
+          <t>RECHAZO PMP1286182</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1286191</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-42283834.4</v>
+        <v>-474381</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>-42283834.4</v>
+        <v>-474381</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1291561</t>
+          <t>RECHAZO PMP1286191</t>
         </is>
       </c>
     </row>
@@ -2136,11 +2160,11 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>PMP1286182</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>-232158</v>
+        <v>-4623481</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -2153,11 +2177,11 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>-232158</v>
+        <v>-4623481</v>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286182</t>
+          <t>RECHAZO PMP1286466</t>
         </is>
       </c>
     </row>
@@ -2169,11 +2193,11 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>PMP1286191</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>-474381</v>
+        <v>-7</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
@@ -2186,11 +2210,11 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>-474381</v>
+        <v>-7</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286191</t>
+          <t>RECHAZO PMP1291558</t>
         </is>
       </c>
     </row>
@@ -2202,11 +2226,11 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>-4623481</v>
+        <v>-94939</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -2219,11 +2243,11 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>-4623481</v>
+        <v>-94939</v>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286466</t>
+          <t>RECHAZO PMP1291559</t>
         </is>
       </c>
     </row>
@@ -2235,11 +2259,11 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>PMP1291558</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>-7</v>
+        <v>-1101</v>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
@@ -2252,11 +2276,11 @@
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>-7</v>
+        <v>-1101</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291558</t>
+          <t>RECHAZO PMP1291560</t>
         </is>
       </c>
     </row>
@@ -2268,11 +2292,11 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>PMP1291559</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>-94939</v>
+        <v>-869290</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -2285,11 +2309,11 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>-94939</v>
+        <v>-869290</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291559</t>
+          <t>RECHAZO PMP1291561</t>
         </is>
       </c>
     </row>
@@ -2301,11 +2325,11 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>PMP1291560</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>-1101</v>
+        <v>-8705</v>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
@@ -2318,11 +2342,11 @@
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>-1101</v>
+        <v>-8705</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291560</t>
+          <t>RECHAZO PMP1291563</t>
         </is>
       </c>
     </row>
@@ -2334,11 +2358,11 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>-869290</v>
+        <v>-153246</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -2351,11 +2375,11 @@
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>-869290</v>
+        <v>-153246</v>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291561</t>
+          <t>RECHAZO PMP1291965</t>
         </is>
       </c>
     </row>
@@ -2367,11 +2391,11 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>PMP1291563</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-8705</v>
+        <v>-608</v>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
@@ -2384,11 +2408,11 @@
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>-8705</v>
+        <v>-608</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291563</t>
+          <t>RECHAZO PMP1292298</t>
         </is>
       </c>
     </row>
@@ -2400,11 +2424,11 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>PMP1291965</t>
+          <t>PMP1292652</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>-153246</v>
+        <v>-143</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -2417,11 +2441,11 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>-153246</v>
+        <v>-143</v>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291965</t>
+          <t>RECHAZO PMP1292652</t>
         </is>
       </c>
     </row>
@@ -2433,11 +2457,11 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>PMP1292298</t>
+          <t>PMP1292654</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>-608</v>
+        <v>-808</v>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
@@ -2450,11 +2474,11 @@
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>-608</v>
+        <v>-808</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292298</t>
+          <t>RECHAZO PMP1292654</t>
         </is>
       </c>
     </row>
@@ -2466,11 +2490,11 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>PMP1292652</t>
+          <t>PMP1292712</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>-143</v>
+        <v>-68</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -2483,11 +2507,11 @@
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>-143</v>
+        <v>-68</v>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292652</t>
+          <t>RECHAZO PMP1292712</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2523,11 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>PMP1292654</t>
+          <t>PMP1292713</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-808</v>
+        <v>-9</v>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
@@ -2516,11 +2540,11 @@
         </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>-808</v>
+        <v>-9</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292654</t>
+          <t>RECHAZO PMP1292713</t>
         </is>
       </c>
     </row>
@@ -2532,11 +2556,11 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>PMP1292712</t>
+          <t>PMP1292714</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>-68</v>
+        <v>-567</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -2549,75 +2573,9 @@
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>-68</v>
+        <v>-567</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1292712</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos Cliente</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>PMP1292713</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>RECHAZO PMP1292713</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos Cliente</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>PMP1292714</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>-567</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>RECHAZO</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>-567</v>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>RECHAZO PMP1292714</t>
         </is>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1858,66 +1858,66 @@
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>4636412647</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-16320</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-16320</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4636412647</t>
+          <t>Myr Vlr Pagado PMP1286466</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>0085501420</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>-11077235</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>-11077235</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>DESCUENTO 0085501420</t>
+          <t>Myr Vlr Pagado PMP1291561</t>
         </is>
       </c>
     </row>
@@ -1929,28 +1929,28 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>9801673296</t>
+          <t>4636412647</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-116500000</v>
+        <v>-16320</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>AVERIA</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>-116500000</v>
+        <v>-16320</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673296</t>
+          <t>AVERIA 4636412647</t>
         </is>
       </c>
     </row>
@@ -1962,68 +1962,68 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>9801673633</t>
+          <t>PMP1286182</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>-296234085</v>
+        <v>-232158</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>-296234085</v>
+        <v>-232158</v>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673633</t>
+          <t>RECHAZO PMP1286182</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1286191</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-70.07999997888692</v>
+        <v>-474381</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>-70.07999997888692</v>
+        <v>-474381</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>RECHAZO PMP1286191</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -2032,57 +2032,57 @@
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>4384856.159999967</v>
+        <v>-4623481</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4384856.159999967</v>
+        <v>-4623481</v>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1286466</t>
+          <t>RECHAZO PMP1286466</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuentos Cliente</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>869392.6000000015</v>
+        <v>-7</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>869392.6000000015</v>
+        <v>-7</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1291561</t>
+          <t>RECHAZO PMP1291558</t>
         </is>
       </c>
     </row>
@@ -2094,11 +2094,11 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>PMP1286182</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>-232158</v>
+        <v>-94939</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>-232158</v>
+        <v>-94939</v>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286182</t>
+          <t>RECHAZO PMP1291559</t>
         </is>
       </c>
     </row>
@@ -2127,11 +2127,11 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>PMP1286191</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-474381</v>
+        <v>-1101</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
@@ -2144,11 +2144,11 @@
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>-474381</v>
+        <v>-1101</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286191</t>
+          <t>RECHAZO PMP1291560</t>
         </is>
       </c>
     </row>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>-4623481</v>
+        <v>-869290</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>-4623481</v>
+        <v>-869290</v>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286466</t>
+          <t>RECHAZO PMP1291561</t>
         </is>
       </c>
     </row>
@@ -2193,11 +2193,11 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>PMP1291558</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>-7</v>
+        <v>-8705</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
@@ -2210,11 +2210,11 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>-7</v>
+        <v>-8705</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291558</t>
+          <t>RECHAZO PMP1291563</t>
         </is>
       </c>
     </row>
@@ -2226,11 +2226,11 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>PMP1291559</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>-94939</v>
+        <v>-153246</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -2243,11 +2243,11 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>-94939</v>
+        <v>-153246</v>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291559</t>
+          <t>RECHAZO PMP1291965</t>
         </is>
       </c>
     </row>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>PMP1291560</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>-1101</v>
+        <v>-608</v>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
@@ -2276,11 +2276,11 @@
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>-1101</v>
+        <v>-608</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291560</t>
+          <t>RECHAZO PMP1292298</t>
         </is>
       </c>
     </row>
@@ -2292,11 +2292,11 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1292652</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>-869290</v>
+        <v>-143</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -2309,11 +2309,11 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>-869290</v>
+        <v>-143</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291561</t>
+          <t>RECHAZO PMP1292652</t>
         </is>
       </c>
     </row>
@@ -2325,11 +2325,11 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>PMP1291563</t>
+          <t>PMP1292654</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>-8705</v>
+        <v>-808</v>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
@@ -2342,11 +2342,11 @@
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>-8705</v>
+        <v>-808</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291563</t>
+          <t>RECHAZO PMP1292654</t>
         </is>
       </c>
     </row>
@@ -2358,11 +2358,11 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>PMP1291965</t>
+          <t>PMP1292712</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>-153246</v>
+        <v>-68</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -2375,11 +2375,11 @@
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>-153246</v>
+        <v>-68</v>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291965</t>
+          <t>RECHAZO PMP1292712</t>
         </is>
       </c>
     </row>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>PMP1292298</t>
+          <t>PMP1292713</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-608</v>
+        <v>-9</v>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
@@ -2408,11 +2408,11 @@
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>-608</v>
+        <v>-9</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292298</t>
+          <t>RECHAZO PMP1292713</t>
         </is>
       </c>
     </row>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>PMP1292652</t>
+          <t>PMP1292714</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>-143</v>
+        <v>-567</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -2441,11 +2441,11 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>-143</v>
+        <v>-567</v>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292652</t>
+          <t>RECHAZO PMP1292714</t>
         </is>
       </c>
     </row>
@@ -2457,28 +2457,28 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>PMP1292654</t>
+          <t>0085501420</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>-808</v>
+        <v>-11077235</v>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>DESCUENTO</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>-808</v>
+        <v>-11077235</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292654</t>
+          <t>DESCUENTO 0085501420</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>PMP1292712</t>
+          <t>9801673296</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>-68</v>
+        <v>-116500000</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>FACT PROVEEDOR</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>-68</v>
+        <v>-116500000</v>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292712</t>
+          <t>FACT PROVEEDOR 9801673296</t>
         </is>
       </c>
     </row>
@@ -2523,61 +2523,61 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>PMP1292713</t>
+          <t>9801673633</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-9</v>
+        <v>-296234085</v>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>FACT PROVEEDOR</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>-9</v>
+        <v>-296234085</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292713</t>
+          <t>FACT PROVEEDOR 9801673633</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>PMP1292714</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>-567</v>
+        <v>-70.07999997888692</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>-567</v>
+        <v>-70.07999997888692</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292714</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_olimpica.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -960,16 +960,16 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>PMP1285642</t>
+          <t>CD4628436910</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>3716132.28</v>
+        <v>43176</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>3716132.28</v>
+        <v>43176</v>
       </c>
       <c r="I19" s="11" t="inlineStr"/>
     </row>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>PMP1285643</t>
+          <t>PMP1285642</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1631086.4</v>
+        <v>3716132.28</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>1631086.4</v>
+        <v>3716132.28</v>
       </c>
       <c r="I20" s="11" t="inlineStr"/>
     </row>
@@ -1002,16 +1002,16 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>PMP1285644</t>
+          <t>PMP1285643</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1953787.6</v>
+        <v>1631086.4</v>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>1953787.6</v>
+        <v>1631086.4</v>
       </c>
       <c r="I21" s="11" t="inlineStr"/>
     </row>
@@ -1023,16 +1023,16 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1285645</t>
+          <t>PMP1285644</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3716132.28</v>
+        <v>1953787.6</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>3716132.28</v>
+        <v>1953787.6</v>
       </c>
       <c r="I22" s="11" t="inlineStr"/>
     </row>
@@ -1044,16 +1044,16 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1286181</t>
+          <t>PMP1285645</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>96593393.26000001</v>
+        <v>3716132.28</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="6" t="n">
-        <v>96593393.26000001</v>
+        <v>3716132.28</v>
       </c>
       <c r="I23" s="11" t="inlineStr"/>
     </row>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1286182</t>
+          <t>PMP1286181</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>70799635.87</v>
+        <v>96593393.26000001</v>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
       <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>70799635.87</v>
+        <v>96593393.26000001</v>
       </c>
       <c r="I24" s="11" t="inlineStr"/>
     </row>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>PMP1286191</t>
+          <t>PMP1286182</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>468865394.64</v>
+        <v>70799635.87</v>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>468865394.64</v>
+        <v>70799635.87</v>
       </c>
       <c r="I25" s="11" t="inlineStr"/>
     </row>
@@ -1107,16 +1107,16 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>PMP1286379</t>
+          <t>PMP1286191</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>15060953.5</v>
+        <v>468865394.64</v>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>15060953.5</v>
+        <v>468865394.64</v>
       </c>
       <c r="I26" s="11" t="inlineStr"/>
     </row>
@@ -1128,16 +1128,16 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PMP1286380</t>
+          <t>PMP1286379</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3569198.36</v>
+        <v>15060953.5</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>3569198.36</v>
+        <v>15060953.5</v>
       </c>
       <c r="I27" s="11" t="inlineStr"/>
     </row>
@@ -1149,16 +1149,16 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>PMP1286421</t>
+          <t>PMP1286380</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>10003422.2</v>
+        <v>3569198.36</v>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="6" t="n">
-        <v>10003422.2</v>
+        <v>3569198.36</v>
       </c>
       <c r="I28" s="11" t="inlineStr"/>
     </row>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>PMP1286422</t>
+          <t>PMP1286421</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>280714498.44</v>
+        <v>10003422.2</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>280714498.44</v>
+        <v>10003422.2</v>
       </c>
       <c r="I29" s="11" t="inlineStr"/>
     </row>
@@ -1191,16 +1191,16 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>PMP1286464</t>
+          <t>PMP1286422</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2371651</v>
+        <v>280714498.44</v>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
       <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="6" t="n">
-        <v>2371651</v>
+        <v>280714498.44</v>
       </c>
       <c r="I30" s="11" t="inlineStr"/>
     </row>
@@ -1212,16 +1212,16 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>PMP1286465</t>
+          <t>PMP1286464</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>62624115.22</v>
+        <v>2371651</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>62624115.22</v>
+        <v>2371651</v>
       </c>
       <c r="I31" s="11" t="inlineStr"/>
     </row>
@@ -1233,16 +1233,16 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1286465</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>640693961.84</v>
+        <v>62624115.22</v>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="6" t="n">
-        <v>640693961.84</v>
+        <v>62624115.22</v>
       </c>
       <c r="I32" s="11" t="inlineStr"/>
     </row>
@@ -1254,16 +1254,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PMP1286467</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>137894507.16</v>
+        <v>640693961.84</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>137894507.16</v>
+        <v>640693961.84</v>
       </c>
       <c r="I33" s="11" t="inlineStr"/>
     </row>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PMP1291552</t>
+          <t>PMP1286467</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4175700</v>
+        <v>137894507.16</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>4175700</v>
+        <v>137894507.16</v>
       </c>
       <c r="I34" s="11" t="inlineStr"/>
     </row>
@@ -1296,16 +1296,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>PMP1291553</t>
+          <t>PMP1291552</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>41784946.6</v>
+        <v>4175700</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>41784946.6</v>
+        <v>4175700</v>
       </c>
       <c r="I35" s="11" t="inlineStr"/>
     </row>
@@ -1317,16 +1317,16 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>PMP1291554</t>
+          <t>PMP1291553</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1230911.12</v>
+        <v>41784946.6</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>1230911.12</v>
+        <v>41784946.6</v>
       </c>
       <c r="I36" s="11" t="inlineStr"/>
     </row>
@@ -1338,16 +1338,16 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PMP1291555</t>
+          <t>PMP1291554</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>347975</v>
+        <v>1230911.12</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>347975</v>
+        <v>1230911.12</v>
       </c>
       <c r="I37" s="11" t="inlineStr"/>
     </row>
@@ -1359,16 +1359,16 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>PMP1291556</t>
+          <t>PMP1291555</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>47200684.8</v>
+        <v>347975</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>47200684.8</v>
+        <v>347975</v>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
     </row>
@@ -1380,16 +1380,16 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMP1291557</t>
+          <t>PMP1291556</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>173988</v>
+        <v>47200684.8</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>173988</v>
+        <v>47200684.8</v>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
     </row>
@@ -1401,16 +1401,16 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>PMP1291558</t>
+          <t>PMP1291557</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>554871.24</v>
+        <v>173988</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>554871.24</v>
+        <v>173988</v>
       </c>
       <c r="I40" s="11" t="inlineStr"/>
     </row>
@@ -1422,16 +1422,16 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>PMP1291559</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7395026.5</v>
+        <v>554871.24</v>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>7395026.5</v>
+        <v>554871.24</v>
       </c>
       <c r="I41" s="11" t="inlineStr"/>
     </row>
@@ -1443,16 +1443,16 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>PMP1291560</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>62932310.75</v>
+        <v>7395026.5</v>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>62932310.75</v>
+        <v>7395026.5</v>
       </c>
       <c r="I42" s="11" t="inlineStr"/>
     </row>
@@ -1464,16 +1464,16 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>43153234.4</v>
+        <v>62932310.75</v>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
       <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>43153234.4</v>
+        <v>62932310.75</v>
       </c>
       <c r="I43" s="11" t="inlineStr"/>
     </row>
@@ -1485,16 +1485,16 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>PMP1291562</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7043898.34</v>
+        <v>43153234.4</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>7043898.34</v>
+        <v>43153234.4</v>
       </c>
       <c r="I44" s="11" t="inlineStr"/>
     </row>
@@ -1506,16 +1506,16 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>PMP1291563</t>
+          <t>PMP1291562</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>82462889.81999999</v>
+        <v>7043898.34</v>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr"/>
       <c r="H45" s="6" t="n">
-        <v>82462889.81999999</v>
+        <v>7043898.34</v>
       </c>
       <c r="I45" s="11" t="inlineStr"/>
     </row>
@@ -1527,16 +1527,16 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>PMP1291965</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7349759</v>
+        <v>82462889.81999999</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>7349759</v>
+        <v>82462889.81999999</v>
       </c>
       <c r="I46" s="11" t="inlineStr"/>
     </row>
@@ -1548,16 +1548,16 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PMP1292294</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>3131775</v>
+        <v>7349759</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>3131775</v>
+        <v>7349759</v>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
     </row>
@@ -1569,16 +1569,16 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>PMP1292295</t>
+          <t>PMP1292294</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>86994</v>
+        <v>3131775</v>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="6" t="n">
-        <v>86994</v>
+        <v>3131775</v>
       </c>
       <c r="I48" s="11" t="inlineStr"/>
     </row>
@@ -1590,16 +1590,16 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>PMP1292296</t>
+          <t>PMP1292295</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>13811678.4</v>
+        <v>86994</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>13811678.4</v>
+        <v>86994</v>
       </c>
       <c r="I49" s="11" t="inlineStr"/>
     </row>
@@ -1611,16 +1611,16 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>PMP1292297</t>
+          <t>PMP1292296</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>32030709.54</v>
+        <v>13811678.4</v>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr"/>
       <c r="H50" s="6" t="n">
-        <v>32030709.54</v>
+        <v>13811678.4</v>
       </c>
       <c r="I50" s="11" t="inlineStr"/>
     </row>
@@ -1632,16 +1632,16 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>PMP1292298</t>
+          <t>PMP1292297</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>34758234.75</v>
+        <v>32030709.54</v>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="6" t="n">
-        <v>34758234.75</v>
+        <v>32030709.54</v>
       </c>
       <c r="I51" s="11" t="inlineStr"/>
     </row>
@@ -1653,16 +1653,16 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>PMP1292309</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>20376764.8</v>
+        <v>34758234.75</v>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
       <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="6" t="n">
-        <v>20376764.8</v>
+        <v>34758234.75</v>
       </c>
       <c r="I52" s="11" t="inlineStr"/>
     </row>
@@ -1674,16 +1674,16 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>PMP1292593</t>
+          <t>PMP1292309</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3131775</v>
+        <v>20376764.8</v>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="6" t="n">
-        <v>3131775</v>
+        <v>20376764.8</v>
       </c>
       <c r="I53" s="11" t="inlineStr"/>
     </row>
@@ -1695,16 +1695,16 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>PMP1292594</t>
+          <t>PMP1292593</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>30380459.6</v>
+        <v>3131775</v>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
       <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="6" t="n">
-        <v>30380459.6</v>
+        <v>3131775</v>
       </c>
       <c r="I54" s="11" t="inlineStr"/>
     </row>
@@ -1716,16 +1716,16 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>PMP1292652</t>
+          <t>PMP1292594</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>30145687</v>
+        <v>30380459.6</v>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="6" t="n">
-        <v>30145687</v>
+        <v>30380459.6</v>
       </c>
       <c r="I55" s="11" t="inlineStr"/>
     </row>
@@ -1737,16 +1737,16 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>PMP1292653</t>
+          <t>PMP1292652</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>27925238.47</v>
+        <v>30145687</v>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
       <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="6" t="n">
-        <v>27925238.47</v>
+        <v>30145687</v>
       </c>
       <c r="I56" s="11" t="inlineStr"/>
     </row>
@@ -1758,16 +1758,16 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>PMP1292654</t>
+          <t>PMP1292653</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>46242233.5</v>
+        <v>27925238.47</v>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
       <c r="G57" s="10" t="inlineStr"/>
       <c r="H57" s="6" t="n">
-        <v>46242233.5</v>
+        <v>27925238.47</v>
       </c>
       <c r="I57" s="11" t="inlineStr"/>
     </row>
@@ -1779,16 +1779,16 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>PMP1292704</t>
+          <t>PMP1292654</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>4192184.8</v>
+        <v>46242233.5</v>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr"/>
       <c r="H58" s="6" t="n">
-        <v>4192184.8</v>
+        <v>46242233.5</v>
       </c>
       <c r="I58" s="11" t="inlineStr"/>
     </row>
@@ -1800,16 +1800,16 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>PMP1292712</t>
+          <t>PMP1292704</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>16403804</v>
+        <v>4192184.8</v>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
       <c r="G59" s="10" t="inlineStr"/>
       <c r="H59" s="6" t="n">
-        <v>16403804</v>
+        <v>4192184.8</v>
       </c>
       <c r="I59" s="11" t="inlineStr"/>
     </row>
@@ -1821,16 +1821,16 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>PMP1292713</t>
+          <t>PMP1292712</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>31007952.84</v>
+        <v>16403804</v>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="6" t="n">
-        <v>31007952.84</v>
+        <v>16403804</v>
       </c>
       <c r="I60" s="11" t="inlineStr"/>
     </row>
@@ -1842,51 +1842,39 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>PMP1292714</t>
+          <t>PMP1292713</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>32461435</v>
+        <v>31007952.84</v>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
       <c r="G61" s="10" t="inlineStr"/>
       <c r="H61" s="6" t="n">
-        <v>32461435</v>
+        <v>31007952.84</v>
       </c>
       <c r="I61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1292714</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>4384856.159999967</v>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>Myr Vlr Pagado</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
+        <v>32461435</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="10" t="inlineStr"/>
       <c r="H62" s="6" t="n">
-        <v>4384856.159999967</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Myr Vlr Pagado PMP1286466</t>
-        </is>
-      </c>
+        <v>32461435</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
@@ -1896,11 +1884,11 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>869392.6000000015</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -1913,44 +1901,44 @@
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>869392.6000000015</v>
+        <v>4384856.159999967</v>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1291561</t>
+          <t>Myr Vlr Pagado PMP1286466</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>4636412647</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-16320</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>-16320</v>
+        <v>869392.6000000015</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4636412647</t>
+          <t>Myr Vlr Pagado PMP1291561</t>
         </is>
       </c>
     </row>
@@ -1962,28 +1950,28 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>PMP1286182</t>
+          <t>4636412647</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>-232158</v>
+        <v>-16320</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>AVERIA</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>-232158</v>
+        <v>-16320</v>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286182</t>
+          <t>AVERIA 4636412647</t>
         </is>
       </c>
     </row>
@@ -1995,11 +1983,11 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>PMP1286191</t>
+          <t>PMP1286182</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-474381</v>
+        <v>-232158</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
@@ -2012,11 +2000,11 @@
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>-474381</v>
+        <v>-232158</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286191</t>
+          <t>RECHAZO PMP1286182</t>
         </is>
       </c>
     </row>
@@ -2028,11 +2016,11 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>PMP1286466</t>
+          <t>PMP1286191</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>-4623481</v>
+        <v>-474381</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -2045,11 +2033,11 @@
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>-4623481</v>
+        <v>-474381</v>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1286466</t>
+          <t>RECHAZO PMP1286191</t>
         </is>
       </c>
     </row>
@@ -2061,11 +2049,11 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>PMP1291558</t>
+          <t>PMP1286466</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>-7</v>
+        <v>-4623481</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
@@ -2078,11 +2066,11 @@
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>-7</v>
+        <v>-4623481</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291558</t>
+          <t>RECHAZO PMP1286466</t>
         </is>
       </c>
     </row>
@@ -2094,11 +2082,11 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>PMP1291559</t>
+          <t>PMP1291558</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>-94939</v>
+        <v>-7</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -2111,11 +2099,11 @@
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>-94939</v>
+        <v>-7</v>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291559</t>
+          <t>RECHAZO PMP1291558</t>
         </is>
       </c>
     </row>
@@ -2127,11 +2115,11 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>PMP1291560</t>
+          <t>PMP1291559</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-1101</v>
+        <v>-94939</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
@@ -2144,11 +2132,11 @@
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>-1101</v>
+        <v>-94939</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291560</t>
+          <t>RECHAZO PMP1291559</t>
         </is>
       </c>
     </row>
@@ -2160,11 +2148,11 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>PMP1291561</t>
+          <t>PMP1291560</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>-869290</v>
+        <v>-1101</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -2177,11 +2165,11 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>-869290</v>
+        <v>-1101</v>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291561</t>
+          <t>RECHAZO PMP1291560</t>
         </is>
       </c>
     </row>
@@ -2193,11 +2181,11 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>PMP1291563</t>
+          <t>PMP1291561</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>-8705</v>
+        <v>-869290</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
@@ -2210,11 +2198,11 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>-8705</v>
+        <v>-869290</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291563</t>
+          <t>RECHAZO PMP1291561</t>
         </is>
       </c>
     </row>
@@ -2226,11 +2214,11 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>PMP1291965</t>
+          <t>PMP1291563</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>-153246</v>
+        <v>-8705</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -2243,11 +2231,11 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>-153246</v>
+        <v>-8705</v>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1291965</t>
+          <t>RECHAZO PMP1291563</t>
         </is>
       </c>
     </row>
@@ -2259,11 +2247,11 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>PMP1292298</t>
+          <t>PMP1291965</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>-608</v>
+        <v>-153246</v>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
@@ -2276,11 +2264,11 @@
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>-608</v>
+        <v>-153246</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292298</t>
+          <t>RECHAZO PMP1291965</t>
         </is>
       </c>
     </row>
@@ -2292,11 +2280,11 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>PMP1292652</t>
+          <t>PMP1292298</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>-143</v>
+        <v>-608</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -2309,11 +2297,11 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>-143</v>
+        <v>-608</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292652</t>
+          <t>RECHAZO PMP1292298</t>
         </is>
       </c>
     </row>
@@ -2325,11 +2313,11 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>PMP1292654</t>
+          <t>PMP1292652</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>-808</v>
+        <v>-143</v>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
@@ -2342,11 +2330,11 @@
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>-808</v>
+        <v>-143</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292654</t>
+          <t>RECHAZO PMP1292652</t>
         </is>
       </c>
     </row>
@@ -2358,11 +2346,11 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>PMP1292712</t>
+          <t>PMP1292654</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>-68</v>
+        <v>-808</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -2375,11 +2363,11 @@
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>-68</v>
+        <v>-808</v>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292712</t>
+          <t>RECHAZO PMP1292654</t>
         </is>
       </c>
     </row>
@@ -2391,11 +2379,11 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>PMP1292713</t>
+          <t>PMP1292712</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-9</v>
+        <v>-68</v>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
@@ -2408,11 +2396,11 @@
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>-9</v>
+        <v>-68</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292713</t>
+          <t>RECHAZO PMP1292712</t>
         </is>
       </c>
     </row>
@@ -2424,11 +2412,11 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>PMP1292714</t>
+          <t>PMP1292713</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>-567</v>
+        <v>-9</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -2441,11 +2429,11 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>-567</v>
+        <v>-9</v>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1292714</t>
+          <t>RECHAZO PMP1292713</t>
         </is>
       </c>
     </row>
@@ -2457,28 +2445,28 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>0085501420</t>
+          <t>PMP1292714</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>-11077235</v>
+        <v>-567</v>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>-11077235</v>
+        <v>-567</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>DESCUENTO 0085501420</t>
+          <t>RECHAZO PMP1292714</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2478,28 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>9801673296</t>
+          <t>0085501420</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>-116500000</v>
+        <v>-11077235</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>DESCUENTO</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>-116500000</v>
+        <v>-11077235</v>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673296</t>
+          <t>DESCUENTO 0085501420</t>
         </is>
       </c>
     </row>
@@ -2523,11 +2511,11 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>9801673633</t>
+          <t>9801673296</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-296234085</v>
+        <v>-116500000</v>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
@@ -2540,42 +2528,75 @@
         </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>-296234085</v>
+        <v>-116500000</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801673633</t>
+          <t>FACT PROVEEDOR 9801673296</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
         <is>
+          <t>Descuentos Cliente</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>9801673633</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>-296234085</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>CSB</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>-296234085</v>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR 9801673633</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="10" t="inlineStr">
+        <is>
           <t>Descuentos Clientes</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E84" s="6" t="n">
         <v>-70.07999997888692</v>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>CSR</t>
         </is>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H84" s="6" t="n">
         <v>-70.07999997888692</v>
       </c>
-      <c r="I83" s="11" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
